--- a/models/glm-5.3/glm-5.3-analysis.xlsx
+++ b/models/glm-5.3/glm-5.3-analysis.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R2471534fb227480d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rd97884c940154e6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rbec15de5aeb844f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Redca9421a40d4d6e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,13 +14,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="8">
     <x:numFmt numFmtId="200" formatCode="0.##"/>
     <x:numFmt numFmtId="201" formatCode="0.0000"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.####"/>
     <x:numFmt numFmtId="203" formatCode="0.000000"/>
+    <x:numFmt numFmtId="204" formatCode="0.0%"/>
+    <x:numFmt numFmtId="205" formatCode="0.000"/>
+    <x:numFmt numFmtId="206" formatCode="0.00%"/>
+    <x:numFmt numFmtId="207" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -41,8 +45,14 @@
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -62,6 +72,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8EEF5"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -99,7 +124,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="55">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -172,10 +197,71 @@
     <x:xf numFmtId="203" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="2">
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA32020"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA32020"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
@@ -4029,7 +4115,1449 @@
       <x:c r="O79" s="30"/>
       <x:c r="P79" s="30"/>
     </x:row>
+    <x:row r="82" ht="23" customHeight="1">
+      <x:c r="A82" s="42" t="str">
+        <x:v>PD 带宽争用耗时评估</x:v>
+      </x:c>
+      <x:c r="B82" s="30"/>
+      <x:c r="C82" s="30"/>
+      <x:c r="D82" s="30"/>
+      <x:c r="E82" s="30"/>
+      <x:c r="F82" s="30"/>
+      <x:c r="G82" s="30"/>
+      <x:c r="H82" s="30"/>
+      <x:c r="I82" s="30"/>
+      <x:c r="J82" s="30"/>
+      <x:c r="K82" s="30"/>
+      <x:c r="L82" s="30"/>
+    </x:row>
+    <x:row r="83" ht="23" customHeight="1">
+      <x:c r="A83" s="30" t="str">
+        <x:v>Prefill 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
+      </x:c>
+      <x:c r="B83" s="30"/>
+      <x:c r="C83" s="30"/>
+      <x:c r="D83" s="30"/>
+      <x:c r="E83" s="30"/>
+      <x:c r="F83" s="30"/>
+      <x:c r="G83" s="30"/>
+      <x:c r="H83" s="30"/>
+      <x:c r="I83" s="30"/>
+      <x:c r="J83" s="30"/>
+      <x:c r="K83" s="30"/>
+      <x:c r="L83" s="30"/>
+    </x:row>
+    <x:row r="84" ht="38" customHeight="1">
+      <x:c r="A84" s="45" t="str">
+        <x:v>带宽降幅</x:v>
+      </x:c>
+      <x:c r="B84" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="C84" s="45" t="str">
+        <x:v>争用覆盖率</x:v>
+      </x:c>
+      <x:c r="D84" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="E84" s="45" t="str">
+        <x:v>基线 forward ms</x:v>
+      </x:c>
+      <x:c r="F84" s="45" t="str">
+        <x:v>实测输入</x:v>
+      </x:c>
+      <x:c r="G84" s="45" t="str">
+        <x:v>默认带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="H84" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="I84" s="30"/>
+      <x:c r="J84" s="30"/>
+      <x:c r="K84" s="30"/>
+      <x:c r="L84" s="30"/>
+    </x:row>
+    <x:row r="85" ht="23" customHeight="1">
+      <x:c r="A85" s="30"/>
+      <x:c r="B85" s="47" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C85" s="30"/>
+      <x:c r="D85" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E85" s="30"/>
+      <x:c r="F85" s="48"/>
+      <x:c r="G85" s="30"/>
+      <x:c r="H85" s="48" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I85" s="30"/>
+      <x:c r="J85" s="30"/>
+      <x:c r="K85" s="30"/>
+      <x:c r="L85" s="30"/>
+    </x:row>
+    <x:row r="86" ht="38" customHeight="1">
+      <x:c r="A86" s="45" t="str">
+        <x:v>通信基线 ms</x:v>
+      </x:c>
+      <x:c r="B86" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="C86" s="45" t="str">
+        <x:v>通信争用后 ms</x:v>
+      </x:c>
+      <x:c r="D86" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="E86" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="F86" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="G86" s="45" t="str">
+        <x:v>forward 新耗时 ms</x:v>
+      </x:c>
+      <x:c r="H86" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="I86" s="45" t="str">
+        <x:v>forward 增幅</x:v>
+      </x:c>
+      <x:c r="J86" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="K86" s="45" t="str">
+        <x:v>输入状态</x:v>
+      </x:c>
+      <x:c r="L86" s="45" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="23" customHeight="1">
+      <x:c r="A87" s="49"/>
+      <x:c r="B87" s="49" t="n">
+        <x:f>SUM(G91:G117)</x:f>
+        <x:v>376.7830528</x:v>
+      </x:c>
+      <x:c r="C87" s="49"/>
+      <x:c r="D87" s="49" t="n">
+        <x:f>SUM(H91:H117)</x:f>
+        <x:v>418.64783644444447</x:v>
+      </x:c>
+      <x:c r="E87" s="49"/>
+      <x:c r="F87" s="49" t="n">
+        <x:f>SUM(K91:K117)</x:f>
+        <x:v>41.86478364444446</x:v>
+      </x:c>
+      <x:c r="G87" s="49"/>
+      <x:c r="H87" s="49" t="str">
+        <x:f>IF(AND(ISNUMBER($F$85),$F$85&gt;0,$F$85&gt;=SUMPRODUCT(G91:G117,J91:J117)),$F$85+F87,"")</x:f>
+      </x:c>
+      <x:c r="I87" s="49"/>
+      <x:c r="J87" s="50" t="str">
+        <x:f>IF(AND(ISNUMBER($F$85),$F$85&gt;0,$F$85&gt;=SUMPRODUCT(G91:G117,J91:J117)),F87/$F$85,"")</x:f>
+      </x:c>
+      <x:c r="K87" s="49"/>
+      <x:c r="L87" s="49" t="str">
+        <x:f>IF($F$85="","待填基线",IF(AND(ISNUMBER($F$85),$F$85&gt;0,$F$85&gt;=SUMPRODUCT(G91:G117,J91:J117)),"已填基线","基线/暴露不一致"))</x:f>
+        <x:v>待填基线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="23" customHeight="1">
+      <x:c r="A88" s="30" t="str">
+        <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
+      </x:c>
+      <x:c r="B88" s="30"/>
+      <x:c r="C88" s="30"/>
+      <x:c r="D88" s="30"/>
+      <x:c r="E88" s="30"/>
+      <x:c r="F88" s="30"/>
+      <x:c r="G88" s="30"/>
+      <x:c r="H88" s="30"/>
+      <x:c r="I88" s="30"/>
+      <x:c r="J88" s="30"/>
+      <x:c r="K88" s="30"/>
+      <x:c r="L88" s="30"/>
+    </x:row>
+    <x:row r="89" ht="23" customHeight="1">
+      <x:c r="A89" s="30" t="str">
+        <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
+      </x:c>
+      <x:c r="B89" s="30"/>
+      <x:c r="C89" s="30"/>
+      <x:c r="D89" s="30"/>
+      <x:c r="E89" s="30"/>
+      <x:c r="F89" s="30"/>
+      <x:c r="G89" s="30"/>
+      <x:c r="H89" s="30"/>
+      <x:c r="I89" s="30"/>
+      <x:c r="J89" s="30"/>
+      <x:c r="K89" s="30"/>
+      <x:c r="L89" s="30"/>
+    </x:row>
+    <x:row r="90" ht="38" customHeight="1">
+      <x:c r="A90" s="45" t="str">
+        <x:v>并行域</x:v>
+      </x:c>
+      <x:c r="B90" s="45" t="str">
+        <x:v>模块</x:v>
+      </x:c>
+      <x:c r="C90" s="45" t="str">
+        <x:v>通信事件</x:v>
+      </x:c>
+      <x:c r="D90" s="45" t="str">
+        <x:v>GB/Rank/Step</x:v>
+      </x:c>
+      <x:c r="E90" s="45" t="str">
+        <x:v>有效带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="F90" s="45" t="str">
+        <x:v>共享比例</x:v>
+      </x:c>
+      <x:c r="G90" s="45" t="str">
+        <x:v>基线带宽项 ms</x:v>
+      </x:c>
+      <x:c r="H90" s="45" t="str">
+        <x:v>争用后带宽项 ms</x:v>
+      </x:c>
+      <x:c r="I90" s="45" t="str">
+        <x:v>通信增量 ms</x:v>
+      </x:c>
+      <x:c r="J90" s="45" t="str">
+        <x:v>暴露系数</x:v>
+      </x:c>
+      <x:c r="K90" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="L90" s="45" t="str">
+        <x:v>公式口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="23" customHeight="1">
+      <x:c r="A91" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B91" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C91" s="30" t="str">
+        <x:v>标准 TP 输出</x:v>
+      </x:c>
+      <x:c r="D91" s="34" t="n">
+        <x:f>(K53*2^20)/1e9</x:f>
+        <x:v>0.176160768</x:v>
+      </x:c>
+      <x:c r="E91" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F91" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G91" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E91),E91&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F91),F91&gt;=0,F91&lt;=1,ISNUMBER(J91),J91&gt;=0,J91&lt;=1),D91/E91*1000,NA())</x:f>
+        <x:v>1.76160768</x:v>
+      </x:c>
+      <x:c r="H91" s="34" t="n">
+        <x:f>G91+I91</x:f>
+        <x:v>1.9573418666666667</x:v>
+      </x:c>
+      <x:c r="I91" s="34" t="n">
+        <x:f>G91*F91*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0.1957341866666667</x:v>
+      </x:c>
+      <x:c r="J91" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K91" s="34" t="n">
+        <x:f>I91*J91</x:f>
+        <x:v>0.1957341866666667</x:v>
+      </x:c>
+      <x:c r="L91" s="30" t="str">
+        <x:v>原通信行 53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="23" customHeight="1">
+      <x:c r="A92" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B92" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C92" s="30" t="str">
+        <x:v>Fine TP Token ID</x:v>
+      </x:c>
+      <x:c r="D92" s="34" t="n">
+        <x:f>(K54*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E92" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F92" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G92" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E92),E92&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F92),F92&gt;=0,F92&lt;=1,ISNUMBER(J92),J92&gt;=0,J92&lt;=1),D92/E92*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H92" s="34" t="n">
+        <x:f>G92+I92</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I92" s="34" t="n">
+        <x:f>G92*F92*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J92" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K92" s="34" t="n">
+        <x:f>I92*J92</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L92" s="30" t="str">
+        <x:v>原通信行 54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="23" customHeight="1">
+      <x:c r="A93" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B93" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C93" s="30" t="str">
+        <x:v>Fine TP Hidden</x:v>
+      </x:c>
+      <x:c r="D93" s="34" t="n">
+        <x:f>(K55*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E93" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F93" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G93" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E93),E93&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F93),F93&gt;=0,F93&lt;=1,ISNUMBER(J93),J93&gt;=0,J93&lt;=1),D93/E93*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H93" s="34" t="n">
+        <x:f>G93+I93</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I93" s="34" t="n">
+        <x:f>G93*F93*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J93" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K93" s="34" t="n">
+        <x:f>I93*J93</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L93" s="30" t="str">
+        <x:v>原通信行 55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="23" customHeight="1">
+      <x:c r="A94" s="30" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B94" s="30" t="str">
+        <x:v>Sparse Attention</x:v>
+      </x:c>
+      <x:c r="C94" s="30" t="str">
+        <x:v>Q/KV 投影输入</x:v>
+      </x:c>
+      <x:c r="D94" s="34" t="n">
+        <x:f>(K56*2^20)/1e9</x:f>
+        <x:v>6.958350336</x:v>
+      </x:c>
+      <x:c r="E94" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F94" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G94" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E94),E94&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F94),F94&gt;=0,F94&lt;=1,ISNUMBER(J94),J94&gt;=0,J94&lt;=1),D94/E94*1000,NA())</x:f>
+        <x:v>69.58350336</x:v>
+      </x:c>
+      <x:c r="H94" s="34" t="n">
+        <x:f>G94+I94</x:f>
+        <x:v>77.31500373333333</x:v>
+      </x:c>
+      <x:c r="I94" s="34" t="n">
+        <x:f>G94*F94*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>7.731500373333333</x:v>
+      </x:c>
+      <x:c r="J94" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K94" s="34" t="n">
+        <x:f>I94*J94</x:f>
+        <x:v>7.731500373333333</x:v>
+      </x:c>
+      <x:c r="L94" s="30" t="str">
+        <x:v>原通信行 56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="23" customHeight="1">
+      <x:c r="A95" s="30" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B95" s="30" t="str">
+        <x:v>Sparse Attention</x:v>
+      </x:c>
+      <x:c r="C95" s="30" t="str">
+        <x:v>恢复 TP Head Layout</x:v>
+      </x:c>
+      <x:c r="D95" s="34" t="n">
+        <x:f>(K57*2^20)/1e9</x:f>
+        <x:v>2.319450112</x:v>
+      </x:c>
+      <x:c r="E95" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F95" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G95" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E95),E95&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F95),F95&gt;=0,F95&lt;=1,ISNUMBER(J95),J95&gt;=0,J95&lt;=1),D95/E95*1000,NA())</x:f>
+        <x:v>23.19450112</x:v>
+      </x:c>
+      <x:c r="H95" s="34" t="n">
+        <x:f>G95+I95</x:f>
+        <x:v>25.771667911111113</x:v>
+      </x:c>
+      <x:c r="I95" s="34" t="n">
+        <x:f>G95*F95*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>2.5771667911111114</x:v>
+      </x:c>
+      <x:c r="J95" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K95" s="34" t="n">
+        <x:f>I95*J95</x:f>
+        <x:v>2.5771667911111114</x:v>
+      </x:c>
+      <x:c r="L95" s="30" t="str">
+        <x:v>原通信行 57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="23" customHeight="1">
+      <x:c r="A96" s="30" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B96" s="30" t="str">
+        <x:v>Indexer</x:v>
+      </x:c>
+      <x:c r="C96" s="30" t="str">
+        <x:v>Top-k Index</x:v>
+      </x:c>
+      <x:c r="D96" s="34" t="n">
+        <x:f>(K58*2^20)/1e9</x:f>
+        <x:v>1.291845632</x:v>
+      </x:c>
+      <x:c r="E96" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F96" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G96" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E96),E96&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F96),F96&gt;=0,F96&lt;=1,ISNUMBER(J96),J96&gt;=0,J96&lt;=1),D96/E96*1000,NA())</x:f>
+        <x:v>12.91845632</x:v>
+      </x:c>
+      <x:c r="H96" s="34" t="n">
+        <x:f>G96+I96</x:f>
+        <x:v>14.353840355555556</x:v>
+      </x:c>
+      <x:c r="I96" s="34" t="n">
+        <x:f>G96*F96*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>1.4353840355555558</x:v>
+      </x:c>
+      <x:c r="J96" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K96" s="34" t="n">
+        <x:f>I96*J96</x:f>
+        <x:v>1.4353840355555558</x:v>
+      </x:c>
+      <x:c r="L96" s="30" t="str">
+        <x:v>原通信行 58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="23" customHeight="1">
+      <x:c r="A97" s="30" t="str">
+        <x:v>O Proj TP</x:v>
+      </x:c>
+      <x:c r="B97" s="30" t="str">
+        <x:v>Sparse Attention</x:v>
+      </x:c>
+      <x:c r="C97" s="30" t="str">
+        <x:v>DSA CP 关闭</x:v>
+      </x:c>
+      <x:c r="D97" s="34" t="n">
+        <x:f>(K59*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E97" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F97" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G97" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E97),E97&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F97),F97&gt;=0,F97&lt;=1,ISNUMBER(J97),J97&gt;=0,J97&lt;=1),D97/E97*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H97" s="34" t="n">
+        <x:f>G97+I97</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I97" s="34" t="n">
+        <x:f>G97*F97*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J97" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K97" s="34" t="n">
+        <x:f>I97*J97</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L97" s="30" t="str">
+        <x:v>原通信行 59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="23" customHeight="1">
+      <x:c r="A98" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B98" s="30" t="str">
+        <x:v>Dense MLP</x:v>
+      </x:c>
+      <x:c r="C98" s="30" t="str">
+        <x:v>Down Proj 输出</x:v>
+      </x:c>
+      <x:c r="D98" s="34" t="n">
+        <x:f>(K60*2^20)/1e9</x:f>
+        <x:v>0.066060288</x:v>
+      </x:c>
+      <x:c r="E98" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F98" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G98" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E98),E98&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F98),F98&gt;=0,F98&lt;=1,ISNUMBER(J98),J98&gt;=0,J98&lt;=1),D98/E98*1000,NA())</x:f>
+        <x:v>0.66060288</x:v>
+      </x:c>
+      <x:c r="H98" s="34" t="n">
+        <x:f>G98+I98</x:f>
+        <x:v>0.7340032</x:v>
+      </x:c>
+      <x:c r="I98" s="34" t="n">
+        <x:f>G98*F98*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0.07340032</x:v>
+      </x:c>
+      <x:c r="J98" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K98" s="34" t="n">
+        <x:f>I98*J98</x:f>
+        <x:v>0.07340032</x:v>
+      </x:c>
+      <x:c r="L98" s="30" t="str">
+        <x:v>原通信行 60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="23" customHeight="1">
+      <x:c r="A99" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B99" s="30" t="str">
+        <x:v>Routed Experts</x:v>
+      </x:c>
+      <x:c r="C99" s="30" t="str">
+        <x:v>Dispatch Hidden</x:v>
+      </x:c>
+      <x:c r="D99" s="34" t="n">
+        <x:f>(K61*2^20)/1e9</x:f>
+        <x:v>6.694109184</x:v>
+      </x:c>
+      <x:c r="E99" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F99" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G99" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E99),E99&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F99),F99&gt;=0,F99&lt;=1,ISNUMBER(J99),J99&gt;=0,J99&lt;=1),D99/E99*1000,NA())</x:f>
+        <x:v>66.94109184000001</x:v>
+      </x:c>
+      <x:c r="H99" s="34" t="n">
+        <x:f>G99+I99</x:f>
+        <x:v>74.37899093333334</x:v>
+      </x:c>
+      <x:c r="I99" s="34" t="n">
+        <x:f>G99*F99*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>7.4378990933333355</x:v>
+      </x:c>
+      <x:c r="J99" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K99" s="34" t="n">
+        <x:f>I99*J99</x:f>
+        <x:v>7.4378990933333355</x:v>
+      </x:c>
+      <x:c r="L99" s="30" t="str">
+        <x:v>原通信行 61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="23" customHeight="1">
+      <x:c r="A100" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B100" s="30" t="str">
+        <x:v>Routed Experts</x:v>
+      </x:c>
+      <x:c r="C100" s="30" t="str">
+        <x:v>Combine Hidden</x:v>
+      </x:c>
+      <x:c r="D100" s="34" t="n">
+        <x:f>(K62*2^20)/1e9</x:f>
+        <x:v>6.694109184</x:v>
+      </x:c>
+      <x:c r="E100" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F100" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G100" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E100),E100&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F100),F100&gt;=0,F100&lt;=1,ISNUMBER(J100),J100&gt;=0,J100&lt;=1),D100/E100*1000,NA())</x:f>
+        <x:v>66.94109184000001</x:v>
+      </x:c>
+      <x:c r="H100" s="34" t="n">
+        <x:f>G100+I100</x:f>
+        <x:v>74.37899093333334</x:v>
+      </x:c>
+      <x:c r="I100" s="34" t="n">
+        <x:f>G100*F100*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>7.4378990933333355</x:v>
+      </x:c>
+      <x:c r="J100" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K100" s="34" t="n">
+        <x:f>I100*J100</x:f>
+        <x:v>7.4378990933333355</x:v>
+      </x:c>
+      <x:c r="L100" s="30" t="str">
+        <x:v>原通信行 62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="23" customHeight="1">
+      <x:c r="A101" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B101" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C101" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D101" s="34" t="n">
+        <x:f>(K63*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E101" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F101" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G101" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E101),E101&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F101),F101&gt;=0,F101&lt;=1,ISNUMBER(J101),J101&gt;=0,J101&lt;=1),D101/E101*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H101" s="34" t="n">
+        <x:f>G101+I101</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I101" s="34" t="n">
+        <x:f>G101*F101*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J101" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K101" s="34" t="n">
+        <x:f>I101*J101</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L101" s="30" t="str">
+        <x:v>原通信行 63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="23" customHeight="1">
+      <x:c r="A102" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B102" s="30" t="str">
+        <x:v>MoE Router</x:v>
+      </x:c>
+      <x:c r="C102" s="30" t="str">
+        <x:v>Router Logits</x:v>
+      </x:c>
+      <x:c r="D102" s="34" t="n">
+        <x:f>(K64*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E102" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F102" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G102" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E102),E102&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F102),F102&gt;=0,F102&lt;=1,ISNUMBER(J102),J102&gt;=0,J102&lt;=1),D102/E102*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H102" s="34" t="n">
+        <x:f>G102+I102</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I102" s="34" t="n">
+        <x:f>G102*F102*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J102" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K102" s="34" t="n">
+        <x:f>I102*J102</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L102" s="30" t="str">
+        <x:v>原通信行 64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="23" customHeight="1">
+      <x:c r="A103" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B103" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C103" s="30" t="str">
+        <x:v>Routed Expert 输出</x:v>
+      </x:c>
+      <x:c r="D103" s="34" t="n">
+        <x:f>(K65*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E103" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F103" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G103" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E103),E103&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F103),F103&gt;=0,F103&lt;=1,ISNUMBER(J103),J103&gt;=0,J103&lt;=1),D103/E103*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H103" s="34" t="n">
+        <x:f>G103+I103</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I103" s="34" t="n">
+        <x:f>G103*F103*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J103" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K103" s="34" t="n">
+        <x:f>I103*J103</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L103" s="30" t="str">
+        <x:v>原通信行 65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="23" customHeight="1">
+      <x:c r="A104" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B104" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C104" s="30" t="str">
+        <x:v>SP 输入</x:v>
+      </x:c>
+      <x:c r="D104" s="34" t="n">
+        <x:f>(K66*2^20)/1e9</x:f>
+        <x:v>6.694109184</x:v>
+      </x:c>
+      <x:c r="E104" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F104" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G104" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E104),E104&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F104),F104&gt;=0,F104&lt;=1,ISNUMBER(J104),J104&gt;=0,J104&lt;=1),D104/E104*1000,NA())</x:f>
+        <x:v>66.94109184000001</x:v>
+      </x:c>
+      <x:c r="H104" s="34" t="n">
+        <x:f>G104+I104</x:f>
+        <x:v>74.37899093333334</x:v>
+      </x:c>
+      <x:c r="I104" s="34" t="n">
+        <x:f>G104*F104*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>7.4378990933333355</x:v>
+      </x:c>
+      <x:c r="J104" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K104" s="34" t="n">
+        <x:f>I104*J104</x:f>
+        <x:v>7.4378990933333355</x:v>
+      </x:c>
+      <x:c r="L104" s="30" t="str">
+        <x:v>原通信行 66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="23" customHeight="1">
+      <x:c r="A105" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B105" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C105" s="30" t="str">
+        <x:v>SP 输出</x:v>
+      </x:c>
+      <x:c r="D105" s="34" t="n">
+        <x:f>(K67*2^20)/1e9</x:f>
+        <x:v>6.694109184</x:v>
+      </x:c>
+      <x:c r="E105" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F105" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G105" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E105),E105&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F105),F105&gt;=0,F105&lt;=1,ISNUMBER(J105),J105&gt;=0,J105&lt;=1),D105/E105*1000,NA())</x:f>
+        <x:v>66.94109184000001</x:v>
+      </x:c>
+      <x:c r="H105" s="34" t="n">
+        <x:f>G105+I105</x:f>
+        <x:v>74.37899093333334</x:v>
+      </x:c>
+      <x:c r="I105" s="34" t="n">
+        <x:f>G105*F105*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>7.4378990933333355</x:v>
+      </x:c>
+      <x:c r="J105" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K105" s="34" t="n">
+        <x:f>I105*J105</x:f>
+        <x:v>7.4378990933333355</x:v>
+      </x:c>
+      <x:c r="L105" s="30" t="str">
+        <x:v>原通信行 67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="23" customHeight="1">
+      <x:c r="A106" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B106" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C106" s="30" t="str">
+        <x:v>非 SP 输出</x:v>
+      </x:c>
+      <x:c r="D106" s="34" t="n">
+        <x:f>(K68*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E106" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F106" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G106" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E106),E106&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F106),F106&gt;=0,F106&lt;=1,ISNUMBER(J106),J106&gt;=0,J106&lt;=1),D106/E106*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H106" s="34" t="n">
+        <x:f>G106+I106</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I106" s="34" t="n">
+        <x:f>G106*F106*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J106" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K106" s="34" t="n">
+        <x:f>I106*J106</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L106" s="30" t="str">
+        <x:v>原通信行 68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="23" customHeight="1">
+      <x:c r="A107" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B107" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C107" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D107" s="34" t="n">
+        <x:f>(K69*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E107" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F107" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G107" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E107),E107&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F107),F107&gt;=0,F107&lt;=1,ISNUMBER(J107),J107&gt;=0,J107&lt;=1),D107/E107*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H107" s="34" t="n">
+        <x:f>G107+I107</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I107" s="34" t="n">
+        <x:f>G107*F107*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J107" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K107" s="34" t="n">
+        <x:f>I107*J107</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L107" s="30" t="str">
+        <x:v>原通信行 69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="23" customHeight="1">
+      <x:c r="A108" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B108" s="30" t="str">
+        <x:v>MoE Router</x:v>
+      </x:c>
+      <x:c r="C108" s="30" t="str">
+        <x:v>Router Logits</x:v>
+      </x:c>
+      <x:c r="D108" s="34" t="n">
+        <x:f>(K70*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E108" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F108" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G108" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E108),E108&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F108),F108&gt;=0,F108&lt;=1,ISNUMBER(J108),J108&gt;=0,J108&lt;=1),D108/E108*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H108" s="34" t="n">
+        <x:f>G108+I108</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I108" s="34" t="n">
+        <x:f>G108*F108*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J108" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K108" s="34" t="n">
+        <x:f>I108*J108</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L108" s="30" t="str">
+        <x:v>原通信行 70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="23" customHeight="1">
+      <x:c r="A109" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B109" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C109" s="30" t="str">
+        <x:v>Routed Expert 输出</x:v>
+      </x:c>
+      <x:c r="D109" s="34" t="n">
+        <x:f>(K71*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E109" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F109" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G109" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E109),E109&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F109),F109&gt;=0,F109&lt;=1,ISNUMBER(J109),J109&gt;=0,J109&lt;=1),D109/E109*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H109" s="34" t="n">
+        <x:f>G109+I109</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I109" s="34" t="n">
+        <x:f>G109*F109*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J109" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K109" s="34" t="n">
+        <x:f>I109*J109</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L109" s="30" t="str">
+        <x:v>原通信行 71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="23" customHeight="1">
+      <x:c r="A110" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B110" s="30" t="str">
+        <x:v>Attention KV</x:v>
+      </x:c>
+      <x:c r="C110" s="30" t="str">
+        <x:v>KV Cache 写入前</x:v>
+      </x:c>
+      <x:c r="D110" s="34" t="n">
+        <x:f>(K72*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E110" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F110" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G110" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E110),E110&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F110),F110&gt;=0,F110&lt;=1,ISNUMBER(J110),J110&gt;=0,J110&lt;=1),D110/E110*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H110" s="34" t="n">
+        <x:f>G110+I110</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I110" s="34" t="n">
+        <x:f>G110*F110*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J110" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K110" s="34" t="n">
+        <x:f>I110*J110</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L110" s="30" t="str">
+        <x:v>原通信行 72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="23" customHeight="1">
+      <x:c r="A111" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B111" s="30" t="str">
+        <x:v>Model Output</x:v>
+      </x:c>
+      <x:c r="C111" s="30" t="str">
+        <x:v>Final Norm 后</x:v>
+      </x:c>
+      <x:c r="D111" s="34" t="n">
+        <x:f>(K73*2^20)/1e9</x:f>
+        <x:v>0.088080384</x:v>
+      </x:c>
+      <x:c r="E111" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F111" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G111" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E111),E111&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F111),F111&gt;=0,F111&lt;=1,ISNUMBER(J111),J111&gt;=0,J111&lt;=1),D111/E111*1000,NA())</x:f>
+        <x:v>0.88080384</x:v>
+      </x:c>
+      <x:c r="H111" s="34" t="n">
+        <x:f>G111+I111</x:f>
+        <x:v>0.9786709333333333</x:v>
+      </x:c>
+      <x:c r="I111" s="34" t="n">
+        <x:f>G111*F111*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0.09786709333333335</x:v>
+      </x:c>
+      <x:c r="J111" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K111" s="34" t="n">
+        <x:f>I111*J111</x:f>
+        <x:v>0.09786709333333335</x:v>
+      </x:c>
+      <x:c r="L111" s="30" t="str">
+        <x:v>原通信行 73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="23" customHeight="1">
+      <x:c r="A112" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B112" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C112" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D112" s="34" t="n">
+        <x:f>(K74*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E112" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F112" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G112" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E112),E112&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F112),F112&gt;=0,F112&lt;=1,ISNUMBER(J112),J112&gt;=0,J112&lt;=1),D112/E112*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H112" s="34" t="n">
+        <x:f>G112+I112</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I112" s="34" t="n">
+        <x:f>G112*F112*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J112" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K112" s="34" t="n">
+        <x:f>I112*J112</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L112" s="30" t="str">
+        <x:v>原通信行 74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="23" customHeight="1">
+      <x:c r="A113" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B113" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C113" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D113" s="34" t="n">
+        <x:f>(K75*2^20)/1e9</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="E113" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F113" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G113" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E113),E113&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F113),F113&gt;=0,F113&lt;=1,ISNUMBER(J113),J113&gt;=0,J113&lt;=1),D113/E113*1000,NA())</x:f>
+        <x:v>0.01376256</x:v>
+      </x:c>
+      <x:c r="H113" s="34" t="n">
+        <x:f>G113+I113</x:f>
+        <x:v>0.015291733333333333</x:v>
+      </x:c>
+      <x:c r="I113" s="34" t="n">
+        <x:f>G113*F113*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0.0015291733333333336</x:v>
+      </x:c>
+      <x:c r="J113" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K113" s="34" t="n">
+        <x:f>I113*J113</x:f>
+        <x:v>0.0015291733333333336</x:v>
+      </x:c>
+      <x:c r="L113" s="30" t="str">
+        <x:v>原通信行 75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="23" customHeight="1">
+      <x:c r="A114" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B114" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C114" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D114" s="34" t="n">
+        <x:f>(K76*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E114" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F114" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G114" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E114),E114&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F114),F114&gt;=0,F114&lt;=1,ISNUMBER(J114),J114&gt;=0,J114&lt;=1),D114/E114*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H114" s="34" t="n">
+        <x:f>G114+I114</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I114" s="34" t="n">
+        <x:f>G114*F114*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J114" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K114" s="34" t="n">
+        <x:f>I114*J114</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L114" s="30" t="str">
+        <x:v>原通信行 76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="23" customHeight="1">
+      <x:c r="A115" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B115" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C115" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D115" s="34" t="n">
+        <x:f>(K77*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E115" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F115" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G115" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E115),E115&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F115),F115&gt;=0,F115&lt;=1,ISNUMBER(J115),J115&gt;=0,J115&lt;=1),D115/E115*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H115" s="34" t="n">
+        <x:f>G115+I115</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I115" s="34" t="n">
+        <x:f>G115*F115*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J115" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K115" s="34" t="n">
+        <x:f>I115*J115</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L115" s="30" t="str">
+        <x:v>原通信行 77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="23" customHeight="1">
+      <x:c r="A116" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B116" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C116" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D116" s="34" t="n">
+        <x:f>(K78*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E116" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F116" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G116" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E116),E116&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F116),F116&gt;=0,F116&lt;=1,ISNUMBER(J116),J116&gt;=0,J116&lt;=1),D116/E116*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H116" s="34" t="n">
+        <x:f>G116+I116</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I116" s="34" t="n">
+        <x:f>G116*F116*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J116" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K116" s="34" t="n">
+        <x:f>I116*J116</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L116" s="30" t="str">
+        <x:v>原通信行 78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="23" customHeight="1">
+      <x:c r="A117" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B117" s="30" t="str">
+        <x:v>MoE 计数</x:v>
+      </x:c>
+      <x:c r="C117" s="30" t="str">
+        <x:v>直方图 Ring AG</x:v>
+      </x:c>
+      <x:c r="D117" s="34" t="n">
+        <x:f>(IF(E61=0,0,H61*ROUNDUP(256/G61,0)*G61*4*(G61-1)))/1e9</x:f>
+        <x:v>0.000544768</x:v>
+      </x:c>
+      <x:c r="E117" s="51" t="n">
+        <x:f>$H$85</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F117" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G117" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E117),E117&gt;0,ISNUMBER($B$85),$B$85&gt;=0,$B$85&lt;1,ISNUMBER($D$85),$D$85&gt;=0,$D$85&lt;=1,ISNUMBER(F117),F117&gt;=0,F117&lt;=1,ISNUMBER(J117),J117&gt;=0,J117&lt;=1),D117/E117*1000,NA())</x:f>
+        <x:v>0.005447680000000001</x:v>
+      </x:c>
+      <x:c r="H117" s="34" t="n">
+        <x:f>G117+I117</x:f>
+        <x:v>0.006052977777777779</x:v>
+      </x:c>
+      <x:c r="I117" s="34" t="n">
+        <x:f>G117*F117*$D$85*$B$85/(1-$B$85)</x:f>
+        <x:v>0.0006052977777777778</x:v>
+      </x:c>
+      <x:c r="J117" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K117" s="34" t="n">
+        <x:f>I117*J117</x:f>
+        <x:v>0.0006052977777777778</x:v>
+      </x:c>
+      <x:c r="L117" s="30" t="str">
+        <x:v>额外控制量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="23" customHeight="1">
+      <x:c r="A118" s="53" t="str">
+        <x:v>所列事件串行相加</x:v>
+      </x:c>
+      <x:c r="B118" s="53"/>
+      <x:c r="C118" s="53"/>
+      <x:c r="D118" s="54" t="n">
+        <x:f>SUM(D91:D117)</x:f>
+        <x:v>37.67830528</x:v>
+      </x:c>
+      <x:c r="E118" s="54"/>
+      <x:c r="F118" s="53"/>
+      <x:c r="G118" s="54" t="n">
+        <x:f>SUM(G91:G117)</x:f>
+        <x:v>376.7830528</x:v>
+      </x:c>
+      <x:c r="H118" s="54" t="n">
+        <x:f>SUM(H91:H117)</x:f>
+        <x:v>418.64783644444447</x:v>
+      </x:c>
+      <x:c r="I118" s="54" t="n">
+        <x:f>SUM(I91:I117)</x:f>
+        <x:v>41.86478364444446</x:v>
+      </x:c>
+      <x:c r="J118" s="53"/>
+      <x:c r="K118" s="54" t="n">
+        <x:f>SUM(K91:K117)</x:f>
+        <x:v>41.86478364444446</x:v>
+      </x:c>
+      <x:c r="L118" s="53"/>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="L87:L87">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="不一致"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -7489,7 +9017,1273 @@
       <x:c r="O75" s="30"/>
       <x:c r="P75" s="30"/>
     </x:row>
+    <x:row r="78" ht="23" customHeight="1">
+      <x:c r="A78" s="42" t="str">
+        <x:v>PD 带宽争用耗时评估</x:v>
+      </x:c>
+      <x:c r="B78" s="30"/>
+      <x:c r="C78" s="30"/>
+      <x:c r="D78" s="30"/>
+      <x:c r="E78" s="30"/>
+      <x:c r="F78" s="30"/>
+      <x:c r="G78" s="30"/>
+      <x:c r="H78" s="30"/>
+      <x:c r="I78" s="30"/>
+      <x:c r="J78" s="30"/>
+      <x:c r="K78" s="30"/>
+      <x:c r="L78" s="30"/>
+    </x:row>
+    <x:row r="79" ht="23" customHeight="1">
+      <x:c r="A79" s="30" t="str">
+        <x:v>Decode 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
+      </x:c>
+      <x:c r="B79" s="30"/>
+      <x:c r="C79" s="30"/>
+      <x:c r="D79" s="30"/>
+      <x:c r="E79" s="30"/>
+      <x:c r="F79" s="30"/>
+      <x:c r="G79" s="30"/>
+      <x:c r="H79" s="30"/>
+      <x:c r="I79" s="30"/>
+      <x:c r="J79" s="30"/>
+      <x:c r="K79" s="30"/>
+      <x:c r="L79" s="30"/>
+    </x:row>
+    <x:row r="80" ht="38" customHeight="1">
+      <x:c r="A80" s="45" t="str">
+        <x:v>带宽降幅</x:v>
+      </x:c>
+      <x:c r="B80" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="C80" s="45" t="str">
+        <x:v>争用覆盖率</x:v>
+      </x:c>
+      <x:c r="D80" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="E80" s="45" t="str">
+        <x:v>基线 forward ms</x:v>
+      </x:c>
+      <x:c r="F80" s="45" t="str">
+        <x:v>实测输入</x:v>
+      </x:c>
+      <x:c r="G80" s="45" t="str">
+        <x:v>默认带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="H80" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="I80" s="30"/>
+      <x:c r="J80" s="30"/>
+      <x:c r="K80" s="30"/>
+      <x:c r="L80" s="30"/>
+    </x:row>
+    <x:row r="81" ht="23" customHeight="1">
+      <x:c r="A81" s="30"/>
+      <x:c r="B81" s="47" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C81" s="30"/>
+      <x:c r="D81" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E81" s="30"/>
+      <x:c r="F81" s="48"/>
+      <x:c r="G81" s="30"/>
+      <x:c r="H81" s="48" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I81" s="30"/>
+      <x:c r="J81" s="30"/>
+      <x:c r="K81" s="30"/>
+      <x:c r="L81" s="30"/>
+    </x:row>
+    <x:row r="82" ht="38" customHeight="1">
+      <x:c r="A82" s="45" t="str">
+        <x:v>通信基线 ms</x:v>
+      </x:c>
+      <x:c r="B82" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="C82" s="45" t="str">
+        <x:v>通信争用后 ms</x:v>
+      </x:c>
+      <x:c r="D82" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="E82" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="F82" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="G82" s="45" t="str">
+        <x:v>forward 新耗时 ms</x:v>
+      </x:c>
+      <x:c r="H82" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="I82" s="45" t="str">
+        <x:v>forward 增幅</x:v>
+      </x:c>
+      <x:c r="J82" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="K82" s="45" t="str">
+        <x:v>输入状态</x:v>
+      </x:c>
+      <x:c r="L82" s="45" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="23" customHeight="1">
+      <x:c r="A83" s="49"/>
+      <x:c r="B83" s="49" t="n">
+        <x:f>SUM(G87:G109)</x:f>
+        <x:v>11.98661632</x:v>
+      </x:c>
+      <x:c r="C83" s="49"/>
+      <x:c r="D83" s="49" t="n">
+        <x:f>SUM(H87:H109)</x:f>
+        <x:v>13.318462577777776</x:v>
+      </x:c>
+      <x:c r="E83" s="49"/>
+      <x:c r="F83" s="49" t="n">
+        <x:f>SUM(K87:K109)</x:f>
+        <x:v>1.331846257777778</x:v>
+      </x:c>
+      <x:c r="G83" s="49"/>
+      <x:c r="H83" s="49" t="str">
+        <x:f>IF(AND(ISNUMBER($F$81),$F$81&gt;0,$F$81&gt;=SUMPRODUCT(G87:G109,J87:J109)),$F$81+F83,"")</x:f>
+      </x:c>
+      <x:c r="I83" s="49"/>
+      <x:c r="J83" s="50" t="str">
+        <x:f>IF(AND(ISNUMBER($F$81),$F$81&gt;0,$F$81&gt;=SUMPRODUCT(G87:G109,J87:J109)),F83/$F$81,"")</x:f>
+      </x:c>
+      <x:c r="K83" s="49"/>
+      <x:c r="L83" s="49" t="str">
+        <x:f>IF($F$81="","待填基线",IF(AND(ISNUMBER($F$81),$F$81&gt;0,$F$81&gt;=SUMPRODUCT(G87:G109,J87:J109)),"已填基线","基线/暴露不一致"))</x:f>
+        <x:v>待填基线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="23" customHeight="1">
+      <x:c r="A84" s="30" t="str">
+        <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
+      </x:c>
+      <x:c r="B84" s="30"/>
+      <x:c r="C84" s="30"/>
+      <x:c r="D84" s="30"/>
+      <x:c r="E84" s="30"/>
+      <x:c r="F84" s="30"/>
+      <x:c r="G84" s="30"/>
+      <x:c r="H84" s="30"/>
+      <x:c r="I84" s="30"/>
+      <x:c r="J84" s="30"/>
+      <x:c r="K84" s="30"/>
+      <x:c r="L84" s="30"/>
+    </x:row>
+    <x:row r="85" ht="23" customHeight="1">
+      <x:c r="A85" s="30" t="str">
+        <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
+      </x:c>
+      <x:c r="B85" s="30"/>
+      <x:c r="C85" s="30"/>
+      <x:c r="D85" s="30"/>
+      <x:c r="E85" s="30"/>
+      <x:c r="F85" s="30"/>
+      <x:c r="G85" s="30"/>
+      <x:c r="H85" s="30"/>
+      <x:c r="I85" s="30"/>
+      <x:c r="J85" s="30"/>
+      <x:c r="K85" s="30"/>
+      <x:c r="L85" s="30"/>
+    </x:row>
+    <x:row r="86" ht="38" customHeight="1">
+      <x:c r="A86" s="45" t="str">
+        <x:v>并行域</x:v>
+      </x:c>
+      <x:c r="B86" s="45" t="str">
+        <x:v>模块</x:v>
+      </x:c>
+      <x:c r="C86" s="45" t="str">
+        <x:v>通信事件</x:v>
+      </x:c>
+      <x:c r="D86" s="45" t="str">
+        <x:v>GB/Rank/Step</x:v>
+      </x:c>
+      <x:c r="E86" s="45" t="str">
+        <x:v>有效带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="F86" s="45" t="str">
+        <x:v>共享比例</x:v>
+      </x:c>
+      <x:c r="G86" s="45" t="str">
+        <x:v>基线带宽项 ms</x:v>
+      </x:c>
+      <x:c r="H86" s="45" t="str">
+        <x:v>争用后带宽项 ms</x:v>
+      </x:c>
+      <x:c r="I86" s="45" t="str">
+        <x:v>通信增量 ms</x:v>
+      </x:c>
+      <x:c r="J86" s="45" t="str">
+        <x:v>暴露系数</x:v>
+      </x:c>
+      <x:c r="K86" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="L86" s="45" t="str">
+        <x:v>公式口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="23" customHeight="1">
+      <x:c r="A87" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B87" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C87" s="30" t="str">
+        <x:v>标准 TP 输出</x:v>
+      </x:c>
+      <x:c r="D87" s="34" t="n">
+        <x:f>(K53*2^20)/1e9</x:f>
+        <x:v>0.005505024</x:v>
+      </x:c>
+      <x:c r="E87" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F87" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G87" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E87),E87&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F87),F87&gt;=0,F87&lt;=1,ISNUMBER(J87),J87&gt;=0,J87&lt;=1),D87/E87*1000,NA())</x:f>
+        <x:v>0.05505024</x:v>
+      </x:c>
+      <x:c r="H87" s="34" t="n">
+        <x:f>G87+I87</x:f>
+        <x:v>0.06116693333333333</x:v>
+      </x:c>
+      <x:c r="I87" s="34" t="n">
+        <x:f>G87*F87*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0.006116693333333334</x:v>
+      </x:c>
+      <x:c r="J87" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K87" s="34" t="n">
+        <x:f>I87*J87</x:f>
+        <x:v>0.006116693333333334</x:v>
+      </x:c>
+      <x:c r="L87" s="30" t="str">
+        <x:v>原通信行 53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="23" customHeight="1">
+      <x:c r="A88" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B88" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C88" s="30" t="str">
+        <x:v>Fine TP Token ID</x:v>
+      </x:c>
+      <x:c r="D88" s="34" t="n">
+        <x:f>(K54*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E88" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F88" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G88" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E88),E88&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F88),F88&gt;=0,F88&lt;=1,ISNUMBER(J88),J88&gt;=0,J88&lt;=1),D88/E88*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H88" s="34" t="n">
+        <x:f>G88+I88</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I88" s="34" t="n">
+        <x:f>G88*F88*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J88" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K88" s="34" t="n">
+        <x:f>I88*J88</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L88" s="30" t="str">
+        <x:v>原通信行 54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="23" customHeight="1">
+      <x:c r="A89" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B89" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C89" s="30" t="str">
+        <x:v>Fine TP Hidden</x:v>
+      </x:c>
+      <x:c r="D89" s="34" t="n">
+        <x:f>(K55*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E89" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F89" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G89" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E89),E89&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F89),F89&gt;=0,F89&lt;=1,ISNUMBER(J89),J89&gt;=0,J89&lt;=1),D89/E89*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H89" s="34" t="n">
+        <x:f>G89+I89</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I89" s="34" t="n">
+        <x:f>G89*F89*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J89" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K89" s="34" t="n">
+        <x:f>I89*J89</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L89" s="30" t="str">
+        <x:v>原通信行 55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="23" customHeight="1">
+      <x:c r="A90" s="30" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B90" s="30" t="str">
+        <x:v>Sparse Attention</x:v>
+      </x:c>
+      <x:c r="C90" s="30" t="str">
+        <x:v>Q/KV 投影输入</x:v>
+      </x:c>
+      <x:c r="D90" s="34" t="n">
+        <x:f>(K56*2^20)/1e9</x:f>
+        <x:v>0.217448448</x:v>
+      </x:c>
+      <x:c r="E90" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F90" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G90" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E90),E90&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F90),F90&gt;=0,F90&lt;=1,ISNUMBER(J90),J90&gt;=0,J90&lt;=1),D90/E90*1000,NA())</x:f>
+        <x:v>2.17448448</x:v>
+      </x:c>
+      <x:c r="H90" s="34" t="n">
+        <x:f>G90+I90</x:f>
+        <x:v>2.4160938666666665</x:v>
+      </x:c>
+      <x:c r="I90" s="34" t="n">
+        <x:f>G90*F90*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0.24160938666666665</x:v>
+      </x:c>
+      <x:c r="J90" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K90" s="34" t="n">
+        <x:f>I90*J90</x:f>
+        <x:v>0.24160938666666665</x:v>
+      </x:c>
+      <x:c r="L90" s="30" t="str">
+        <x:v>原通信行 56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="23" customHeight="1">
+      <x:c r="A91" s="30" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B91" s="30" t="str">
+        <x:v>Sparse Attention</x:v>
+      </x:c>
+      <x:c r="C91" s="30" t="str">
+        <x:v>恢复 TP Head Layout</x:v>
+      </x:c>
+      <x:c r="D91" s="34" t="n">
+        <x:f>(K57*2^20)/1e9</x:f>
+        <x:v>0.072482816</x:v>
+      </x:c>
+      <x:c r="E91" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F91" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G91" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E91),E91&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F91),F91&gt;=0,F91&lt;=1,ISNUMBER(J91),J91&gt;=0,J91&lt;=1),D91/E91*1000,NA())</x:f>
+        <x:v>0.72482816</x:v>
+      </x:c>
+      <x:c r="H91" s="34" t="n">
+        <x:f>G91+I91</x:f>
+        <x:v>0.8053646222222223</x:v>
+      </x:c>
+      <x:c r="I91" s="34" t="n">
+        <x:f>G91*F91*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0.08053646222222223</x:v>
+      </x:c>
+      <x:c r="J91" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K91" s="34" t="n">
+        <x:f>I91*J91</x:f>
+        <x:v>0.08053646222222223</x:v>
+      </x:c>
+      <x:c r="L91" s="30" t="str">
+        <x:v>原通信行 57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="23" customHeight="1">
+      <x:c r="A92" s="30" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B92" s="30" t="str">
+        <x:v>Indexer</x:v>
+      </x:c>
+      <x:c r="C92" s="30" t="str">
+        <x:v>Top-k Index</x:v>
+      </x:c>
+      <x:c r="D92" s="34" t="n">
+        <x:f>(K58*2^20)/1e9</x:f>
+        <x:v>0.040370176</x:v>
+      </x:c>
+      <x:c r="E92" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F92" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G92" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E92),E92&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F92),F92&gt;=0,F92&lt;=1,ISNUMBER(J92),J92&gt;=0,J92&lt;=1),D92/E92*1000,NA())</x:f>
+        <x:v>0.40370176</x:v>
+      </x:c>
+      <x:c r="H92" s="34" t="n">
+        <x:f>G92+I92</x:f>
+        <x:v>0.44855751111111114</x:v>
+      </x:c>
+      <x:c r="I92" s="34" t="n">
+        <x:f>G92*F92*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0.04485575111111112</x:v>
+      </x:c>
+      <x:c r="J92" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K92" s="34" t="n">
+        <x:f>I92*J92</x:f>
+        <x:v>0.04485575111111112</x:v>
+      </x:c>
+      <x:c r="L92" s="30" t="str">
+        <x:v>原通信行 58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="23" customHeight="1">
+      <x:c r="A93" s="30" t="str">
+        <x:v>O Proj TP</x:v>
+      </x:c>
+      <x:c r="B93" s="30" t="str">
+        <x:v>Sparse Attention</x:v>
+      </x:c>
+      <x:c r="C93" s="30" t="str">
+        <x:v>DSA CP 关闭</x:v>
+      </x:c>
+      <x:c r="D93" s="34" t="n">
+        <x:f>(K59*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E93" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F93" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G93" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E93),E93&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F93),F93&gt;=0,F93&lt;=1,ISNUMBER(J93),J93&gt;=0,J93&lt;=1),D93/E93*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H93" s="34" t="n">
+        <x:f>G93+I93</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I93" s="34" t="n">
+        <x:f>G93*F93*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J93" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K93" s="34" t="n">
+        <x:f>I93*J93</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L93" s="30" t="str">
+        <x:v>原通信行 59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="23" customHeight="1">
+      <x:c r="A94" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B94" s="30" t="str">
+        <x:v>Dense MLP</x:v>
+      </x:c>
+      <x:c r="C94" s="30" t="str">
+        <x:v>Down Proj 输出</x:v>
+      </x:c>
+      <x:c r="D94" s="34" t="n">
+        <x:f>(K60*2^20)/1e9</x:f>
+        <x:v>0.002064384</x:v>
+      </x:c>
+      <x:c r="E94" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F94" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G94" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E94),E94&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F94),F94&gt;=0,F94&lt;=1,ISNUMBER(J94),J94&gt;=0,J94&lt;=1),D94/E94*1000,NA())</x:f>
+        <x:v>0.02064384</x:v>
+      </x:c>
+      <x:c r="H94" s="34" t="n">
+        <x:f>G94+I94</x:f>
+        <x:v>0.0229376</x:v>
+      </x:c>
+      <x:c r="I94" s="34" t="n">
+        <x:f>G94*F94*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0.00229376</x:v>
+      </x:c>
+      <x:c r="J94" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K94" s="34" t="n">
+        <x:f>I94*J94</x:f>
+        <x:v>0.00229376</x:v>
+      </x:c>
+      <x:c r="L94" s="30" t="str">
+        <x:v>原通信行 60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="23" customHeight="1">
+      <x:c r="A95" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B95" s="30" t="str">
+        <x:v>Routed Experts</x:v>
+      </x:c>
+      <x:c r="C95" s="30" t="str">
+        <x:v>MC2 FullMesh Dispatch</x:v>
+      </x:c>
+      <x:c r="D95" s="34" t="n">
+        <x:f>(IF(F61=2,E61/6144*H61*(ROUNDUP((ROUNDUP(6144*F61/32,0)*32+32)/480,0)*512),NA()))/1e9</x:f>
+        <x:v>0.226623488</x:v>
+      </x:c>
+      <x:c r="E95" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F95" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G95" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E95),E95&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F95),F95&gt;=0,F95&lt;=1,ISNUMBER(J95),J95&gt;=0,J95&lt;=1),D95/E95*1000,NA())</x:f>
+        <x:v>2.2662348800000003</x:v>
+      </x:c>
+      <x:c r="H95" s="34" t="n">
+        <x:f>G95+I95</x:f>
+        <x:v>2.5180387555555557</x:v>
+      </x:c>
+      <x:c r="I95" s="34" t="n">
+        <x:f>G95*F95*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0.2518038755555556</x:v>
+      </x:c>
+      <x:c r="J95" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K95" s="34" t="n">
+        <x:f>I95*J95</x:f>
+        <x:v>0.2518038755555556</x:v>
+      </x:c>
+      <x:c r="L95" s="30" t="str">
+        <x:v>原通信行 61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="23" customHeight="1">
+      <x:c r="A96" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B96" s="30" t="str">
+        <x:v>Routed Experts</x:v>
+      </x:c>
+      <x:c r="C96" s="30" t="str">
+        <x:v>MC2 Combine + flags</x:v>
+      </x:c>
+      <x:c r="D96" s="34" t="n">
+        <x:f>(IF(F62=2,K62*2^20+E62/6144*H62*32,NA()))/1e9</x:f>
+        <x:v>0.20973568</x:v>
+      </x:c>
+      <x:c r="E96" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F96" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G96" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E96),E96&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F96),F96&gt;=0,F96&lt;=1,ISNUMBER(J96),J96&gt;=0,J96&lt;=1),D96/E96*1000,NA())</x:f>
+        <x:v>2.0973568</x:v>
+      </x:c>
+      <x:c r="H96" s="34" t="n">
+        <x:f>G96+I96</x:f>
+        <x:v>2.3303964444444443</x:v>
+      </x:c>
+      <x:c r="I96" s="34" t="n">
+        <x:f>G96*F96*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0.23303964444444444</x:v>
+      </x:c>
+      <x:c r="J96" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K96" s="34" t="n">
+        <x:f>I96*J96</x:f>
+        <x:v>0.23303964444444444</x:v>
+      </x:c>
+      <x:c r="L96" s="30" t="str">
+        <x:v>原通信行 62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="23" customHeight="1">
+      <x:c r="A97" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B97" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C97" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D97" s="34" t="n">
+        <x:f>(K63*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E97" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F97" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G97" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E97),E97&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F97),F97&gt;=0,F97&lt;=1,ISNUMBER(J97),J97&gt;=0,J97&lt;=1),D97/E97*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H97" s="34" t="n">
+        <x:f>G97+I97</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I97" s="34" t="n">
+        <x:f>G97*F97*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J97" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K97" s="34" t="n">
+        <x:f>I97*J97</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L97" s="30" t="str">
+        <x:v>原通信行 63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="23" customHeight="1">
+      <x:c r="A98" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B98" s="30" t="str">
+        <x:v>MoE Router</x:v>
+      </x:c>
+      <x:c r="C98" s="30" t="str">
+        <x:v>Router Logits</x:v>
+      </x:c>
+      <x:c r="D98" s="34" t="n">
+        <x:f>(K64*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E98" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F98" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G98" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E98),E98&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F98),F98&gt;=0,F98&lt;=1,ISNUMBER(J98),J98&gt;=0,J98&lt;=1),D98/E98*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H98" s="34" t="n">
+        <x:f>G98+I98</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I98" s="34" t="n">
+        <x:f>G98*F98*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J98" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K98" s="34" t="n">
+        <x:f>I98*J98</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L98" s="30" t="str">
+        <x:v>原通信行 64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="23" customHeight="1">
+      <x:c r="A99" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B99" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C99" s="30" t="str">
+        <x:v>Routed Expert 输出</x:v>
+      </x:c>
+      <x:c r="D99" s="34" t="n">
+        <x:f>(K65*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E99" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F99" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G99" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E99),E99&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F99),F99&gt;=0,F99&lt;=1,ISNUMBER(J99),J99&gt;=0,J99&lt;=1),D99/E99*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H99" s="34" t="n">
+        <x:f>G99+I99</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I99" s="34" t="n">
+        <x:f>G99*F99*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J99" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K99" s="34" t="n">
+        <x:f>I99*J99</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L99" s="30" t="str">
+        <x:v>原通信行 65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="23" customHeight="1">
+      <x:c r="A100" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B100" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C100" s="30" t="str">
+        <x:v>SP 输入</x:v>
+      </x:c>
+      <x:c r="D100" s="34" t="n">
+        <x:f>(K66*2^20)/1e9</x:f>
+        <x:v>0.209190912</x:v>
+      </x:c>
+      <x:c r="E100" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F100" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G100" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E100),E100&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F100),F100&gt;=0,F100&lt;=1,ISNUMBER(J100),J100&gt;=0,J100&lt;=1),D100/E100*1000,NA())</x:f>
+        <x:v>2.0919091200000004</x:v>
+      </x:c>
+      <x:c r="H100" s="34" t="n">
+        <x:f>G100+I100</x:f>
+        <x:v>2.324343466666667</x:v>
+      </x:c>
+      <x:c r="I100" s="34" t="n">
+        <x:f>G100*F100*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0.23243434666666674</x:v>
+      </x:c>
+      <x:c r="J100" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K100" s="34" t="n">
+        <x:f>I100*J100</x:f>
+        <x:v>0.23243434666666674</x:v>
+      </x:c>
+      <x:c r="L100" s="30" t="str">
+        <x:v>原通信行 66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="23" customHeight="1">
+      <x:c r="A101" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B101" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C101" s="30" t="str">
+        <x:v>SP 输出</x:v>
+      </x:c>
+      <x:c r="D101" s="34" t="n">
+        <x:f>(K67*2^20)/1e9</x:f>
+        <x:v>0.209190912</x:v>
+      </x:c>
+      <x:c r="E101" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F101" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G101" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E101),E101&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F101),F101&gt;=0,F101&lt;=1,ISNUMBER(J101),J101&gt;=0,J101&lt;=1),D101/E101*1000,NA())</x:f>
+        <x:v>2.0919091200000004</x:v>
+      </x:c>
+      <x:c r="H101" s="34" t="n">
+        <x:f>G101+I101</x:f>
+        <x:v>2.324343466666667</x:v>
+      </x:c>
+      <x:c r="I101" s="34" t="n">
+        <x:f>G101*F101*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0.23243434666666674</x:v>
+      </x:c>
+      <x:c r="J101" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K101" s="34" t="n">
+        <x:f>I101*J101</x:f>
+        <x:v>0.23243434666666674</x:v>
+      </x:c>
+      <x:c r="L101" s="30" t="str">
+        <x:v>原通信行 67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="23" customHeight="1">
+      <x:c r="A102" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B102" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C102" s="30" t="str">
+        <x:v>非 SP 输出</x:v>
+      </x:c>
+      <x:c r="D102" s="34" t="n">
+        <x:f>(K68*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E102" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F102" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G102" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E102),E102&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F102),F102&gt;=0,F102&lt;=1,ISNUMBER(J102),J102&gt;=0,J102&lt;=1),D102/E102*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H102" s="34" t="n">
+        <x:f>G102+I102</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I102" s="34" t="n">
+        <x:f>G102*F102*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J102" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K102" s="34" t="n">
+        <x:f>I102*J102</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L102" s="30" t="str">
+        <x:v>原通信行 68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="23" customHeight="1">
+      <x:c r="A103" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B103" s="30" t="str">
+        <x:v>Model Output</x:v>
+      </x:c>
+      <x:c r="C103" s="30" t="str">
+        <x:v>Final Norm 后</x:v>
+      </x:c>
+      <x:c r="D103" s="34" t="n">
+        <x:f>(K69*2^20)/1e9</x:f>
+        <x:v>0.002752512</x:v>
+      </x:c>
+      <x:c r="E103" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F103" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G103" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E103),E103&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F103),F103&gt;=0,F103&lt;=1,ISNUMBER(J103),J103&gt;=0,J103&lt;=1),D103/E103*1000,NA())</x:f>
+        <x:v>0.02752512</x:v>
+      </x:c>
+      <x:c r="H103" s="34" t="n">
+        <x:f>G103+I103</x:f>
+        <x:v>0.030583466666666666</x:v>
+      </x:c>
+      <x:c r="I103" s="34" t="n">
+        <x:f>G103*F103*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0.003058346666666667</x:v>
+      </x:c>
+      <x:c r="J103" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K103" s="34" t="n">
+        <x:f>I103*J103</x:f>
+        <x:v>0.003058346666666667</x:v>
+      </x:c>
+      <x:c r="L103" s="30" t="str">
+        <x:v>原通信行 69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="23" customHeight="1">
+      <x:c r="A104" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B104" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C104" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D104" s="34" t="n">
+        <x:f>(K70*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E104" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F104" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G104" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E104),E104&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F104),F104&gt;=0,F104&lt;=1,ISNUMBER(J104),J104&gt;=0,J104&lt;=1),D104/E104*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H104" s="34" t="n">
+        <x:f>G104+I104</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I104" s="34" t="n">
+        <x:f>G104*F104*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J104" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K104" s="34" t="n">
+        <x:f>I104*J104</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L104" s="30" t="str">
+        <x:v>原通信行 70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="23" customHeight="1">
+      <x:c r="A105" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B105" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C105" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D105" s="34" t="n">
+        <x:f>(K71*2^20)/1e9</x:f>
+        <x:v>0.002752512</x:v>
+      </x:c>
+      <x:c r="E105" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F105" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G105" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E105),E105&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F105),F105&gt;=0,F105&lt;=1,ISNUMBER(J105),J105&gt;=0,J105&lt;=1),D105/E105*1000,NA())</x:f>
+        <x:v>0.02752512</x:v>
+      </x:c>
+      <x:c r="H105" s="34" t="n">
+        <x:f>G105+I105</x:f>
+        <x:v>0.030583466666666666</x:v>
+      </x:c>
+      <x:c r="I105" s="34" t="n">
+        <x:f>G105*F105*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0.003058346666666667</x:v>
+      </x:c>
+      <x:c r="J105" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K105" s="34" t="n">
+        <x:f>I105*J105</x:f>
+        <x:v>0.003058346666666667</x:v>
+      </x:c>
+      <x:c r="L105" s="30" t="str">
+        <x:v>原通信行 71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="23" customHeight="1">
+      <x:c r="A106" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B106" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C106" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D106" s="34" t="n">
+        <x:f>(K72*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E106" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F106" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G106" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E106),E106&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F106),F106&gt;=0,F106&lt;=1,ISNUMBER(J106),J106&gt;=0,J106&lt;=1),D106/E106*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H106" s="34" t="n">
+        <x:f>G106+I106</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I106" s="34" t="n">
+        <x:f>G106*F106*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J106" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K106" s="34" t="n">
+        <x:f>I106*J106</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L106" s="30" t="str">
+        <x:v>原通信行 72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="23" customHeight="1">
+      <x:c r="A107" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B107" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C107" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D107" s="34" t="n">
+        <x:f>(K73*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E107" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F107" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G107" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E107),E107&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F107),F107&gt;=0,F107&lt;=1,ISNUMBER(J107),J107&gt;=0,J107&lt;=1),D107/E107*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H107" s="34" t="n">
+        <x:f>G107+I107</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I107" s="34" t="n">
+        <x:f>G107*F107*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J107" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K107" s="34" t="n">
+        <x:f>I107*J107</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L107" s="30" t="str">
+        <x:v>原通信行 73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="23" customHeight="1">
+      <x:c r="A108" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B108" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C108" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D108" s="34" t="n">
+        <x:f>(K74*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E108" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F108" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G108" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E108),E108&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F108),F108&gt;=0,F108&lt;=1,ISNUMBER(J108),J108&gt;=0,J108&lt;=1),D108/E108*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H108" s="34" t="n">
+        <x:f>G108+I108</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I108" s="34" t="n">
+        <x:f>G108*F108*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J108" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K108" s="34" t="n">
+        <x:f>I108*J108</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L108" s="30" t="str">
+        <x:v>原通信行 74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="23" customHeight="1">
+      <x:c r="A109" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B109" s="30" t="str">
+        <x:v>MoE 计数</x:v>
+      </x:c>
+      <x:c r="C109" s="30" t="str">
+        <x:v>MC2 count 写入</x:v>
+      </x:c>
+      <x:c r="D109" s="34" t="n">
+        <x:f>(IF(E61=0,0,H61*ROUNDUP(256/G61,0)*(G61-1)*32))/1e9</x:f>
+        <x:v>0.000544768</x:v>
+      </x:c>
+      <x:c r="E109" s="51" t="n">
+        <x:f>$H$81</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F109" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G109" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E109),E109&gt;0,ISNUMBER($B$81),$B$81&gt;=0,$B$81&lt;1,ISNUMBER($D$81),$D$81&gt;=0,$D$81&lt;=1,ISNUMBER(F109),F109&gt;=0,F109&lt;=1,ISNUMBER(J109),J109&gt;=0,J109&lt;=1),D109/E109*1000,NA())</x:f>
+        <x:v>0.005447680000000001</x:v>
+      </x:c>
+      <x:c r="H109" s="34" t="n">
+        <x:f>G109+I109</x:f>
+        <x:v>0.006052977777777779</x:v>
+      </x:c>
+      <x:c r="I109" s="34" t="n">
+        <x:f>G109*F109*$D$81*$B$81/(1-$B$81)</x:f>
+        <x:v>0.0006052977777777778</x:v>
+      </x:c>
+      <x:c r="J109" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K109" s="34" t="n">
+        <x:f>I109*J109</x:f>
+        <x:v>0.0006052977777777778</x:v>
+      </x:c>
+      <x:c r="L109" s="30" t="str">
+        <x:v>额外控制量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="23" customHeight="1">
+      <x:c r="A110" s="53" t="str">
+        <x:v>所列事件串行相加</x:v>
+      </x:c>
+      <x:c r="B110" s="53"/>
+      <x:c r="C110" s="53"/>
+      <x:c r="D110" s="54" t="n">
+        <x:f>SUM(D87:D109)</x:f>
+        <x:v>1.1986616319999999</x:v>
+      </x:c>
+      <x:c r="E110" s="54"/>
+      <x:c r="F110" s="53"/>
+      <x:c r="G110" s="54" t="n">
+        <x:f>SUM(G87:G109)</x:f>
+        <x:v>11.98661632</x:v>
+      </x:c>
+      <x:c r="H110" s="54" t="n">
+        <x:f>SUM(H87:H109)</x:f>
+        <x:v>13.318462577777776</x:v>
+      </x:c>
+      <x:c r="I110" s="54" t="n">
+        <x:f>SUM(I87:I109)</x:f>
+        <x:v>1.331846257777778</x:v>
+      </x:c>
+      <x:c r="J110" s="53"/>
+      <x:c r="K110" s="54" t="n">
+        <x:f>SUM(K87:K109)</x:f>
+        <x:v>1.331846257777778</x:v>
+      </x:c>
+      <x:c r="L110" s="53"/>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="L83:L83">
+    <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="不一致"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/models/glm-5.3/glm-5.3-analysis.xlsx
+++ b/models/glm-5.3/glm-5.3-analysis.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rbec15de5aeb844f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Redca9421a40d4d6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rfcf28e90223d42ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Ra1a32d12811a49b8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52,7 +52,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -87,6 +87,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8EEF5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -124,7 +129,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="55">
+  <x:cellXfs count="65">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -236,6 +241,36 @@
     <x:xf numFmtId="203" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -246,7 +281,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -256,7 +291,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -4115,8 +4150,8 @@
       <x:c r="O79" s="30"/>
       <x:c r="P79" s="30"/>
     </x:row>
-    <x:row r="82" ht="23" customHeight="1">
-      <x:c r="A82" s="42" t="str">
+    <x:row r="82" ht="15" customHeight="1">
+      <x:c r="A82" s="40" t="str">
         <x:v>PD 带宽争用耗时评估</x:v>
       </x:c>
       <x:c r="B82" s="30"/>
@@ -4131,7 +4166,7 @@
       <x:c r="K82" s="30"/>
       <x:c r="L82" s="30"/>
     </x:row>
-    <x:row r="83" ht="23" customHeight="1">
+    <x:row r="83" ht="15" customHeight="1">
       <x:c r="A83" s="30" t="str">
         <x:v>Prefill 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
       </x:c>
@@ -4147,29 +4182,29 @@
       <x:c r="K83" s="30"/>
       <x:c r="L83" s="30"/>
     </x:row>
-    <x:row r="84" ht="38" customHeight="1">
-      <x:c r="A84" s="45" t="str">
+    <x:row r="84" ht="30" customHeight="1">
+      <x:c r="A84" s="62" t="str">
         <x:v>带宽降幅</x:v>
       </x:c>
-      <x:c r="B84" s="45" t="str">
+      <x:c r="B84" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="C84" s="45" t="str">
+      <x:c r="C84" s="62" t="str">
         <x:v>争用覆盖率</x:v>
       </x:c>
-      <x:c r="D84" s="45" t="str">
+      <x:c r="D84" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="E84" s="45" t="str">
+      <x:c r="E84" s="62" t="str">
         <x:v>基线 forward ms</x:v>
       </x:c>
-      <x:c r="F84" s="45" t="str">
+      <x:c r="F84" s="62" t="str">
         <x:v>实测输入</x:v>
       </x:c>
-      <x:c r="G84" s="45" t="str">
+      <x:c r="G84" s="62" t="str">
         <x:v>默认带宽 GB/s</x:v>
       </x:c>
-      <x:c r="H84" s="45" t="str">
+      <x:c r="H84" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
       <x:c r="I84" s="30"/>
@@ -4177,19 +4212,19 @@
       <x:c r="K84" s="30"/>
       <x:c r="L84" s="30"/>
     </x:row>
-    <x:row r="85" ht="23" customHeight="1">
+    <x:row r="85" ht="15" customHeight="1">
       <x:c r="A85" s="30"/>
-      <x:c r="B85" s="47" t="n">
+      <x:c r="B85" s="63" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C85" s="30"/>
-      <x:c r="D85" s="47" t="n">
+      <x:c r="D85" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E85" s="30"/>
-      <x:c r="F85" s="48"/>
+      <x:c r="F85" s="38"/>
       <x:c r="G85" s="30"/>
-      <x:c r="H85" s="48" t="n">
+      <x:c r="H85" s="36" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I85" s="30"/>
@@ -4197,45 +4232,45 @@
       <x:c r="K85" s="30"/>
       <x:c r="L85" s="30"/>
     </x:row>
-    <x:row r="86" ht="38" customHeight="1">
-      <x:c r="A86" s="45" t="str">
+    <x:row r="86" ht="30" customHeight="1">
+      <x:c r="A86" s="62" t="str">
         <x:v>通信基线 ms</x:v>
       </x:c>
-      <x:c r="B86" s="45" t="str">
+      <x:c r="B86" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="C86" s="45" t="str">
+      <x:c r="C86" s="62" t="str">
         <x:v>通信争用后 ms</x:v>
       </x:c>
-      <x:c r="D86" s="45" t="str">
+      <x:c r="D86" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="E86" s="45" t="str">
+      <x:c r="E86" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="F86" s="45" t="str">
+      <x:c r="F86" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="G86" s="45" t="str">
+      <x:c r="G86" s="62" t="str">
         <x:v>forward 新耗时 ms</x:v>
       </x:c>
-      <x:c r="H86" s="45" t="str">
+      <x:c r="H86" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="I86" s="45" t="str">
+      <x:c r="I86" s="62" t="str">
         <x:v>forward 增幅</x:v>
       </x:c>
-      <x:c r="J86" s="45" t="str">
+      <x:c r="J86" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="K86" s="45" t="str">
+      <x:c r="K86" s="62" t="str">
         <x:v>输入状态</x:v>
       </x:c>
-      <x:c r="L86" s="45" t="str">
+      <x:c r="L86" s="62" t="str">
         <x:v>状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="23" customHeight="1">
+    <x:row r="87" ht="15" customHeight="1">
       <x:c r="A87" s="49"/>
       <x:c r="B87" s="49" t="n">
         <x:f>SUM(G91:G117)</x:f>
@@ -4265,7 +4300,7 @@
         <x:v>待填基线</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="23" customHeight="1">
+    <x:row r="88" ht="15" customHeight="1">
       <x:c r="A88" s="30" t="str">
         <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
       </x:c>
@@ -4281,7 +4316,7 @@
       <x:c r="K88" s="30"/>
       <x:c r="L88" s="30"/>
     </x:row>
-    <x:row r="89" ht="23" customHeight="1">
+    <x:row r="89" ht="15" customHeight="1">
       <x:c r="A89" s="30" t="str">
         <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
       </x:c>
@@ -4297,45 +4332,45 @@
       <x:c r="K89" s="30"/>
       <x:c r="L89" s="30"/>
     </x:row>
-    <x:row r="90" ht="38" customHeight="1">
-      <x:c r="A90" s="45" t="str">
+    <x:row r="90" ht="30" customHeight="1">
+      <x:c r="A90" s="62" t="str">
         <x:v>并行域</x:v>
       </x:c>
-      <x:c r="B90" s="45" t="str">
+      <x:c r="B90" s="62" t="str">
         <x:v>模块</x:v>
       </x:c>
-      <x:c r="C90" s="45" t="str">
+      <x:c r="C90" s="62" t="str">
         <x:v>通信事件</x:v>
       </x:c>
-      <x:c r="D90" s="45" t="str">
+      <x:c r="D90" s="62" t="str">
         <x:v>GB/Rank/Step</x:v>
       </x:c>
-      <x:c r="E90" s="45" t="str">
+      <x:c r="E90" s="62" t="str">
         <x:v>有效带宽 GB/s</x:v>
       </x:c>
-      <x:c r="F90" s="45" t="str">
+      <x:c r="F90" s="62" t="str">
         <x:v>共享比例</x:v>
       </x:c>
-      <x:c r="G90" s="45" t="str">
+      <x:c r="G90" s="62" t="str">
         <x:v>基线带宽项 ms</x:v>
       </x:c>
-      <x:c r="H90" s="45" t="str">
+      <x:c r="H90" s="62" t="str">
         <x:v>争用后带宽项 ms</x:v>
       </x:c>
-      <x:c r="I90" s="45" t="str">
+      <x:c r="I90" s="62" t="str">
         <x:v>通信增量 ms</x:v>
       </x:c>
-      <x:c r="J90" s="45" t="str">
+      <x:c r="J90" s="62" t="str">
         <x:v>暴露系数</x:v>
       </x:c>
-      <x:c r="K90" s="45" t="str">
+      <x:c r="K90" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="L90" s="45" t="str">
+      <x:c r="L90" s="62" t="str">
         <x:v>公式口径</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="23" customHeight="1">
+    <x:row r="91" ht="15" customHeight="1">
       <x:c r="A91" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -4349,11 +4384,11 @@
         <x:f>(K53*2^20)/1e9</x:f>
         <x:v>0.176160768</x:v>
       </x:c>
-      <x:c r="E91" s="51" t="n">
+      <x:c r="E91" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F91" s="52" t="n">
+      <x:c r="F91" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G91" s="34" t="n">
@@ -4368,7 +4403,7 @@
         <x:f>G91*F91*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0.1957341866666667</x:v>
       </x:c>
-      <x:c r="J91" s="52" t="n">
+      <x:c r="J91" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K91" s="34" t="n">
@@ -4379,7 +4414,7 @@
         <x:v>原通信行 53</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="23" customHeight="1">
+    <x:row r="92" ht="15" customHeight="1">
       <x:c r="A92" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -4393,11 +4428,11 @@
         <x:f>(K54*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E92" s="51" t="n">
+      <x:c r="E92" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F92" s="52" t="n">
+      <x:c r="F92" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G92" s="34" t="n">
@@ -4412,7 +4447,7 @@
         <x:f>G92*F92*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J92" s="52" t="n">
+      <x:c r="J92" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K92" s="34" t="n">
@@ -4423,7 +4458,7 @@
         <x:v>原通信行 54</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="23" customHeight="1">
+    <x:row r="93" ht="15" customHeight="1">
       <x:c r="A93" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -4437,11 +4472,11 @@
         <x:f>(K55*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E93" s="51" t="n">
+      <x:c r="E93" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F93" s="52" t="n">
+      <x:c r="F93" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G93" s="34" t="n">
@@ -4456,7 +4491,7 @@
         <x:f>G93*F93*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J93" s="52" t="n">
+      <x:c r="J93" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K93" s="34" t="n">
@@ -4467,7 +4502,7 @@
         <x:v>原通信行 55</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="23" customHeight="1">
+    <x:row r="94" ht="15" customHeight="1">
       <x:c r="A94" s="30" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -4481,11 +4516,11 @@
         <x:f>(K56*2^20)/1e9</x:f>
         <x:v>6.958350336</x:v>
       </x:c>
-      <x:c r="E94" s="51" t="n">
+      <x:c r="E94" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F94" s="52" t="n">
+      <x:c r="F94" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G94" s="34" t="n">
@@ -4500,7 +4535,7 @@
         <x:f>G94*F94*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>7.731500373333333</x:v>
       </x:c>
-      <x:c r="J94" s="52" t="n">
+      <x:c r="J94" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K94" s="34" t="n">
@@ -4511,7 +4546,7 @@
         <x:v>原通信行 56</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="23" customHeight="1">
+    <x:row r="95" ht="15" customHeight="1">
       <x:c r="A95" s="30" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -4525,11 +4560,11 @@
         <x:f>(K57*2^20)/1e9</x:f>
         <x:v>2.319450112</x:v>
       </x:c>
-      <x:c r="E95" s="51" t="n">
+      <x:c r="E95" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F95" s="52" t="n">
+      <x:c r="F95" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G95" s="34" t="n">
@@ -4544,7 +4579,7 @@
         <x:f>G95*F95*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>2.5771667911111114</x:v>
       </x:c>
-      <x:c r="J95" s="52" t="n">
+      <x:c r="J95" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K95" s="34" t="n">
@@ -4555,7 +4590,7 @@
         <x:v>原通信行 57</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="23" customHeight="1">
+    <x:row r="96" ht="15" customHeight="1">
       <x:c r="A96" s="30" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -4569,11 +4604,11 @@
         <x:f>(K58*2^20)/1e9</x:f>
         <x:v>1.291845632</x:v>
       </x:c>
-      <x:c r="E96" s="51" t="n">
+      <x:c r="E96" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F96" s="52" t="n">
+      <x:c r="F96" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G96" s="34" t="n">
@@ -4588,7 +4623,7 @@
         <x:f>G96*F96*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>1.4353840355555558</x:v>
       </x:c>
-      <x:c r="J96" s="52" t="n">
+      <x:c r="J96" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K96" s="34" t="n">
@@ -4599,7 +4634,7 @@
         <x:v>原通信行 58</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="23" customHeight="1">
+    <x:row r="97" ht="15" customHeight="1">
       <x:c r="A97" s="30" t="str">
         <x:v>O Proj TP</x:v>
       </x:c>
@@ -4613,11 +4648,11 @@
         <x:f>(K59*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E97" s="51" t="n">
+      <x:c r="E97" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F97" s="52" t="n">
+      <x:c r="F97" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G97" s="34" t="n">
@@ -4632,7 +4667,7 @@
         <x:f>G97*F97*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J97" s="52" t="n">
+      <x:c r="J97" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K97" s="34" t="n">
@@ -4643,7 +4678,7 @@
         <x:v>原通信行 59</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="23" customHeight="1">
+    <x:row r="98" ht="15" customHeight="1">
       <x:c r="A98" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -4657,11 +4692,11 @@
         <x:f>(K60*2^20)/1e9</x:f>
         <x:v>0.066060288</x:v>
       </x:c>
-      <x:c r="E98" s="51" t="n">
+      <x:c r="E98" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F98" s="52" t="n">
+      <x:c r="F98" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G98" s="34" t="n">
@@ -4676,7 +4711,7 @@
         <x:f>G98*F98*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0.07340032</x:v>
       </x:c>
-      <x:c r="J98" s="52" t="n">
+      <x:c r="J98" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K98" s="34" t="n">
@@ -4687,7 +4722,7 @@
         <x:v>原通信行 60</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="23" customHeight="1">
+    <x:row r="99" ht="15" customHeight="1">
       <x:c r="A99" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -4701,11 +4736,11 @@
         <x:f>(K61*2^20)/1e9</x:f>
         <x:v>6.694109184</x:v>
       </x:c>
-      <x:c r="E99" s="51" t="n">
+      <x:c r="E99" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F99" s="52" t="n">
+      <x:c r="F99" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G99" s="34" t="n">
@@ -4720,7 +4755,7 @@
         <x:f>G99*F99*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>7.4378990933333355</x:v>
       </x:c>
-      <x:c r="J99" s="52" t="n">
+      <x:c r="J99" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K99" s="34" t="n">
@@ -4731,7 +4766,7 @@
         <x:v>原通信行 61</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="23" customHeight="1">
+    <x:row r="100" ht="15" customHeight="1">
       <x:c r="A100" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -4745,11 +4780,11 @@
         <x:f>(K62*2^20)/1e9</x:f>
         <x:v>6.694109184</x:v>
       </x:c>
-      <x:c r="E100" s="51" t="n">
+      <x:c r="E100" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F100" s="52" t="n">
+      <x:c r="F100" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G100" s="34" t="n">
@@ -4764,7 +4799,7 @@
         <x:f>G100*F100*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>7.4378990933333355</x:v>
       </x:c>
-      <x:c r="J100" s="52" t="n">
+      <x:c r="J100" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K100" s="34" t="n">
@@ -4775,7 +4810,7 @@
         <x:v>原通信行 62</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="23" customHeight="1">
+    <x:row r="101" ht="15" customHeight="1">
       <x:c r="A101" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -4789,11 +4824,11 @@
         <x:f>(K63*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E101" s="51" t="n">
+      <x:c r="E101" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F101" s="52" t="n">
+      <x:c r="F101" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G101" s="34" t="n">
@@ -4808,7 +4843,7 @@
         <x:f>G101*F101*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J101" s="52" t="n">
+      <x:c r="J101" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K101" s="34" t="n">
@@ -4819,7 +4854,7 @@
         <x:v>原通信行 63</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="23" customHeight="1">
+    <x:row r="102" ht="15" customHeight="1">
       <x:c r="A102" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -4833,11 +4868,11 @@
         <x:f>(K64*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E102" s="51" t="n">
+      <x:c r="E102" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F102" s="52" t="n">
+      <x:c r="F102" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G102" s="34" t="n">
@@ -4852,7 +4887,7 @@
         <x:f>G102*F102*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J102" s="52" t="n">
+      <x:c r="J102" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K102" s="34" t="n">
@@ -4863,7 +4898,7 @@
         <x:v>原通信行 64</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="23" customHeight="1">
+    <x:row r="103" ht="15" customHeight="1">
       <x:c r="A103" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -4877,11 +4912,11 @@
         <x:f>(K65*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E103" s="51" t="n">
+      <x:c r="E103" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F103" s="52" t="n">
+      <x:c r="F103" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G103" s="34" t="n">
@@ -4896,7 +4931,7 @@
         <x:f>G103*F103*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J103" s="52" t="n">
+      <x:c r="J103" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K103" s="34" t="n">
@@ -4907,7 +4942,7 @@
         <x:v>原通信行 65</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="23" customHeight="1">
+    <x:row r="104" ht="15" customHeight="1">
       <x:c r="A104" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -4921,11 +4956,11 @@
         <x:f>(K66*2^20)/1e9</x:f>
         <x:v>6.694109184</x:v>
       </x:c>
-      <x:c r="E104" s="51" t="n">
+      <x:c r="E104" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F104" s="52" t="n">
+      <x:c r="F104" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G104" s="34" t="n">
@@ -4940,7 +4975,7 @@
         <x:f>G104*F104*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>7.4378990933333355</x:v>
       </x:c>
-      <x:c r="J104" s="52" t="n">
+      <x:c r="J104" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K104" s="34" t="n">
@@ -4951,7 +4986,7 @@
         <x:v>原通信行 66</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="23" customHeight="1">
+    <x:row r="105" ht="15" customHeight="1">
       <x:c r="A105" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -4965,11 +5000,11 @@
         <x:f>(K67*2^20)/1e9</x:f>
         <x:v>6.694109184</x:v>
       </x:c>
-      <x:c r="E105" s="51" t="n">
+      <x:c r="E105" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F105" s="52" t="n">
+      <x:c r="F105" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G105" s="34" t="n">
@@ -4984,7 +5019,7 @@
         <x:f>G105*F105*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>7.4378990933333355</x:v>
       </x:c>
-      <x:c r="J105" s="52" t="n">
+      <x:c r="J105" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K105" s="34" t="n">
@@ -4995,7 +5030,7 @@
         <x:v>原通信行 67</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="23" customHeight="1">
+    <x:row r="106" ht="15" customHeight="1">
       <x:c r="A106" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -5009,11 +5044,11 @@
         <x:f>(K68*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E106" s="51" t="n">
+      <x:c r="E106" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F106" s="52" t="n">
+      <x:c r="F106" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G106" s="34" t="n">
@@ -5028,7 +5063,7 @@
         <x:f>G106*F106*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J106" s="52" t="n">
+      <x:c r="J106" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K106" s="34" t="n">
@@ -5039,7 +5074,7 @@
         <x:v>原通信行 68</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="23" customHeight="1">
+    <x:row r="107" ht="15" customHeight="1">
       <x:c r="A107" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -5053,11 +5088,11 @@
         <x:f>(K69*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E107" s="51" t="n">
+      <x:c r="E107" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F107" s="52" t="n">
+      <x:c r="F107" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G107" s="34" t="n">
@@ -5072,7 +5107,7 @@
         <x:f>G107*F107*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J107" s="52" t="n">
+      <x:c r="J107" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K107" s="34" t="n">
@@ -5083,7 +5118,7 @@
         <x:v>原通信行 69</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="23" customHeight="1">
+    <x:row r="108" ht="15" customHeight="1">
       <x:c r="A108" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -5097,11 +5132,11 @@
         <x:f>(K70*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E108" s="51" t="n">
+      <x:c r="E108" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F108" s="52" t="n">
+      <x:c r="F108" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G108" s="34" t="n">
@@ -5116,7 +5151,7 @@
         <x:f>G108*F108*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J108" s="52" t="n">
+      <x:c r="J108" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K108" s="34" t="n">
@@ -5127,7 +5162,7 @@
         <x:v>原通信行 70</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="23" customHeight="1">
+    <x:row r="109" ht="15" customHeight="1">
       <x:c r="A109" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -5141,11 +5176,11 @@
         <x:f>(K71*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E109" s="51" t="n">
+      <x:c r="E109" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F109" s="52" t="n">
+      <x:c r="F109" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G109" s="34" t="n">
@@ -5160,7 +5195,7 @@
         <x:f>G109*F109*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J109" s="52" t="n">
+      <x:c r="J109" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K109" s="34" t="n">
@@ -5171,7 +5206,7 @@
         <x:v>原通信行 71</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="23" customHeight="1">
+    <x:row r="110" ht="15" customHeight="1">
       <x:c r="A110" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -5185,11 +5220,11 @@
         <x:f>(K72*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E110" s="51" t="n">
+      <x:c r="E110" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F110" s="52" t="n">
+      <x:c r="F110" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G110" s="34" t="n">
@@ -5204,7 +5239,7 @@
         <x:f>G110*F110*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J110" s="52" t="n">
+      <x:c r="J110" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K110" s="34" t="n">
@@ -5215,7 +5250,7 @@
         <x:v>原通信行 72</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="23" customHeight="1">
+    <x:row r="111" ht="15" customHeight="1">
       <x:c r="A111" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -5229,11 +5264,11 @@
         <x:f>(K73*2^20)/1e9</x:f>
         <x:v>0.088080384</x:v>
       </x:c>
-      <x:c r="E111" s="51" t="n">
+      <x:c r="E111" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F111" s="52" t="n">
+      <x:c r="F111" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G111" s="34" t="n">
@@ -5248,7 +5283,7 @@
         <x:f>G111*F111*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0.09786709333333335</x:v>
       </x:c>
-      <x:c r="J111" s="52" t="n">
+      <x:c r="J111" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K111" s="34" t="n">
@@ -5259,7 +5294,7 @@
         <x:v>原通信行 73</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="23" customHeight="1">
+    <x:row r="112" ht="15" customHeight="1">
       <x:c r="A112" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -5273,11 +5308,11 @@
         <x:f>(K74*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E112" s="51" t="n">
+      <x:c r="E112" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F112" s="52" t="n">
+      <x:c r="F112" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G112" s="34" t="n">
@@ -5292,7 +5327,7 @@
         <x:f>G112*F112*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J112" s="52" t="n">
+      <x:c r="J112" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K112" s="34" t="n">
@@ -5303,7 +5338,7 @@
         <x:v>原通信行 74</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="23" customHeight="1">
+    <x:row r="113" ht="15" customHeight="1">
       <x:c r="A113" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -5317,11 +5352,11 @@
         <x:f>(K75*2^20)/1e9</x:f>
         <x:v>0.001376256</x:v>
       </x:c>
-      <x:c r="E113" s="51" t="n">
+      <x:c r="E113" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F113" s="52" t="n">
+      <x:c r="F113" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G113" s="34" t="n">
@@ -5336,7 +5371,7 @@
         <x:f>G113*F113*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0.0015291733333333336</x:v>
       </x:c>
-      <x:c r="J113" s="52" t="n">
+      <x:c r="J113" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K113" s="34" t="n">
@@ -5347,7 +5382,7 @@
         <x:v>原通信行 75</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="23" customHeight="1">
+    <x:row r="114" ht="15" customHeight="1">
       <x:c r="A114" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -5361,11 +5396,11 @@
         <x:f>(K76*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E114" s="51" t="n">
+      <x:c r="E114" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F114" s="52" t="n">
+      <x:c r="F114" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G114" s="34" t="n">
@@ -5380,7 +5415,7 @@
         <x:f>G114*F114*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J114" s="52" t="n">
+      <x:c r="J114" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K114" s="34" t="n">
@@ -5391,7 +5426,7 @@
         <x:v>原通信行 76</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="23" customHeight="1">
+    <x:row r="115" ht="15" customHeight="1">
       <x:c r="A115" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -5405,11 +5440,11 @@
         <x:f>(K77*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E115" s="51" t="n">
+      <x:c r="E115" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F115" s="52" t="n">
+      <x:c r="F115" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G115" s="34" t="n">
@@ -5424,7 +5459,7 @@
         <x:f>G115*F115*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J115" s="52" t="n">
+      <x:c r="J115" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K115" s="34" t="n">
@@ -5435,7 +5470,7 @@
         <x:v>原通信行 77</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="23" customHeight="1">
+    <x:row r="116" ht="15" customHeight="1">
       <x:c r="A116" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -5449,11 +5484,11 @@
         <x:f>(K78*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E116" s="51" t="n">
+      <x:c r="E116" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F116" s="52" t="n">
+      <x:c r="F116" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G116" s="34" t="n">
@@ -5468,7 +5503,7 @@
         <x:f>G116*F116*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J116" s="52" t="n">
+      <x:c r="J116" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K116" s="34" t="n">
@@ -5479,7 +5514,7 @@
         <x:v>原通信行 78</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="23" customHeight="1">
+    <x:row r="117" ht="15" customHeight="1">
       <x:c r="A117" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -5493,11 +5528,11 @@
         <x:f>(IF(E61=0,0,H61*ROUNDUP(256/G61,0)*G61*4*(G61-1)))/1e9</x:f>
         <x:v>0.000544768</x:v>
       </x:c>
-      <x:c r="E117" s="51" t="n">
+      <x:c r="E117" s="64" t="n">
         <x:f>$H$85</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F117" s="52" t="n">
+      <x:c r="F117" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G117" s="34" t="n">
@@ -5512,7 +5547,7 @@
         <x:f>G117*F117*$D$85*$B$85/(1-$B$85)</x:f>
         <x:v>0.0006052977777777778</x:v>
       </x:c>
-      <x:c r="J117" s="52" t="n">
+      <x:c r="J117" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K117" s="34" t="n">
@@ -5523,36 +5558,36 @@
         <x:v>额外控制量</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="23" customHeight="1">
-      <x:c r="A118" s="53" t="str">
+    <x:row r="118" ht="15" customHeight="1">
+      <x:c r="A118" s="40" t="str">
         <x:v>所列事件串行相加</x:v>
       </x:c>
-      <x:c r="B118" s="53"/>
-      <x:c r="C118" s="53"/>
-      <x:c r="D118" s="54" t="n">
+      <x:c r="B118" s="40"/>
+      <x:c r="C118" s="40"/>
+      <x:c r="D118" s="41" t="n">
         <x:f>SUM(D91:D117)</x:f>
         <x:v>37.67830528</x:v>
       </x:c>
-      <x:c r="E118" s="54"/>
-      <x:c r="F118" s="53"/>
-      <x:c r="G118" s="54" t="n">
+      <x:c r="E118" s="40"/>
+      <x:c r="F118" s="40"/>
+      <x:c r="G118" s="41" t="n">
         <x:f>SUM(G91:G117)</x:f>
         <x:v>376.7830528</x:v>
       </x:c>
-      <x:c r="H118" s="54" t="n">
+      <x:c r="H118" s="41" t="n">
         <x:f>SUM(H91:H117)</x:f>
         <x:v>418.64783644444447</x:v>
       </x:c>
-      <x:c r="I118" s="54" t="n">
+      <x:c r="I118" s="41" t="n">
         <x:f>SUM(I91:I117)</x:f>
         <x:v>41.86478364444446</x:v>
       </x:c>
-      <x:c r="J118" s="53"/>
-      <x:c r="K118" s="54" t="n">
+      <x:c r="J118" s="40"/>
+      <x:c r="K118" s="41" t="n">
         <x:f>SUM(K91:K117)</x:f>
         <x:v>41.86478364444446</x:v>
       </x:c>
-      <x:c r="L118" s="53"/>
+      <x:c r="L118" s="40"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="L87:L87">
@@ -9017,8 +9052,8 @@
       <x:c r="O75" s="30"/>
       <x:c r="P75" s="30"/>
     </x:row>
-    <x:row r="78" ht="23" customHeight="1">
-      <x:c r="A78" s="42" t="str">
+    <x:row r="78" ht="15" customHeight="1">
+      <x:c r="A78" s="40" t="str">
         <x:v>PD 带宽争用耗时评估</x:v>
       </x:c>
       <x:c r="B78" s="30"/>
@@ -9033,7 +9068,7 @@
       <x:c r="K78" s="30"/>
       <x:c r="L78" s="30"/>
     </x:row>
-    <x:row r="79" ht="23" customHeight="1">
+    <x:row r="79" ht="15" customHeight="1">
       <x:c r="A79" s="30" t="str">
         <x:v>Decode 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
       </x:c>
@@ -9049,29 +9084,29 @@
       <x:c r="K79" s="30"/>
       <x:c r="L79" s="30"/>
     </x:row>
-    <x:row r="80" ht="38" customHeight="1">
-      <x:c r="A80" s="45" t="str">
+    <x:row r="80" ht="30" customHeight="1">
+      <x:c r="A80" s="62" t="str">
         <x:v>带宽降幅</x:v>
       </x:c>
-      <x:c r="B80" s="45" t="str">
+      <x:c r="B80" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="C80" s="45" t="str">
+      <x:c r="C80" s="62" t="str">
         <x:v>争用覆盖率</x:v>
       </x:c>
-      <x:c r="D80" s="45" t="str">
+      <x:c r="D80" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="E80" s="45" t="str">
+      <x:c r="E80" s="62" t="str">
         <x:v>基线 forward ms</x:v>
       </x:c>
-      <x:c r="F80" s="45" t="str">
+      <x:c r="F80" s="62" t="str">
         <x:v>实测输入</x:v>
       </x:c>
-      <x:c r="G80" s="45" t="str">
+      <x:c r="G80" s="62" t="str">
         <x:v>默认带宽 GB/s</x:v>
       </x:c>
-      <x:c r="H80" s="45" t="str">
+      <x:c r="H80" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
       <x:c r="I80" s="30"/>
@@ -9079,19 +9114,19 @@
       <x:c r="K80" s="30"/>
       <x:c r="L80" s="30"/>
     </x:row>
-    <x:row r="81" ht="23" customHeight="1">
+    <x:row r="81" ht="15" customHeight="1">
       <x:c r="A81" s="30"/>
-      <x:c r="B81" s="47" t="n">
+      <x:c r="B81" s="63" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C81" s="30"/>
-      <x:c r="D81" s="47" t="n">
+      <x:c r="D81" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E81" s="30"/>
-      <x:c r="F81" s="48"/>
+      <x:c r="F81" s="38"/>
       <x:c r="G81" s="30"/>
-      <x:c r="H81" s="48" t="n">
+      <x:c r="H81" s="36" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I81" s="30"/>
@@ -9099,45 +9134,45 @@
       <x:c r="K81" s="30"/>
       <x:c r="L81" s="30"/>
     </x:row>
-    <x:row r="82" ht="38" customHeight="1">
-      <x:c r="A82" s="45" t="str">
+    <x:row r="82" ht="30" customHeight="1">
+      <x:c r="A82" s="62" t="str">
         <x:v>通信基线 ms</x:v>
       </x:c>
-      <x:c r="B82" s="45" t="str">
+      <x:c r="B82" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="C82" s="45" t="str">
+      <x:c r="C82" s="62" t="str">
         <x:v>通信争用后 ms</x:v>
       </x:c>
-      <x:c r="D82" s="45" t="str">
+      <x:c r="D82" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="E82" s="45" t="str">
+      <x:c r="E82" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="F82" s="45" t="str">
+      <x:c r="F82" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="G82" s="45" t="str">
+      <x:c r="G82" s="62" t="str">
         <x:v>forward 新耗时 ms</x:v>
       </x:c>
-      <x:c r="H82" s="45" t="str">
+      <x:c r="H82" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="I82" s="45" t="str">
+      <x:c r="I82" s="62" t="str">
         <x:v>forward 增幅</x:v>
       </x:c>
-      <x:c r="J82" s="45" t="str">
+      <x:c r="J82" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="K82" s="45" t="str">
+      <x:c r="K82" s="62" t="str">
         <x:v>输入状态</x:v>
       </x:c>
-      <x:c r="L82" s="45" t="str">
+      <x:c r="L82" s="62" t="str">
         <x:v>状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="23" customHeight="1">
+    <x:row r="83" ht="15" customHeight="1">
       <x:c r="A83" s="49"/>
       <x:c r="B83" s="49" t="n">
         <x:f>SUM(G87:G109)</x:f>
@@ -9167,7 +9202,7 @@
         <x:v>待填基线</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="23" customHeight="1">
+    <x:row r="84" ht="15" customHeight="1">
       <x:c r="A84" s="30" t="str">
         <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
       </x:c>
@@ -9183,7 +9218,7 @@
       <x:c r="K84" s="30"/>
       <x:c r="L84" s="30"/>
     </x:row>
-    <x:row r="85" ht="23" customHeight="1">
+    <x:row r="85" ht="15" customHeight="1">
       <x:c r="A85" s="30" t="str">
         <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
       </x:c>
@@ -9199,45 +9234,45 @@
       <x:c r="K85" s="30"/>
       <x:c r="L85" s="30"/>
     </x:row>
-    <x:row r="86" ht="38" customHeight="1">
-      <x:c r="A86" s="45" t="str">
+    <x:row r="86" ht="30" customHeight="1">
+      <x:c r="A86" s="62" t="str">
         <x:v>并行域</x:v>
       </x:c>
-      <x:c r="B86" s="45" t="str">
+      <x:c r="B86" s="62" t="str">
         <x:v>模块</x:v>
       </x:c>
-      <x:c r="C86" s="45" t="str">
+      <x:c r="C86" s="62" t="str">
         <x:v>通信事件</x:v>
       </x:c>
-      <x:c r="D86" s="45" t="str">
+      <x:c r="D86" s="62" t="str">
         <x:v>GB/Rank/Step</x:v>
       </x:c>
-      <x:c r="E86" s="45" t="str">
+      <x:c r="E86" s="62" t="str">
         <x:v>有效带宽 GB/s</x:v>
       </x:c>
-      <x:c r="F86" s="45" t="str">
+      <x:c r="F86" s="62" t="str">
         <x:v>共享比例</x:v>
       </x:c>
-      <x:c r="G86" s="45" t="str">
+      <x:c r="G86" s="62" t="str">
         <x:v>基线带宽项 ms</x:v>
       </x:c>
-      <x:c r="H86" s="45" t="str">
+      <x:c r="H86" s="62" t="str">
         <x:v>争用后带宽项 ms</x:v>
       </x:c>
-      <x:c r="I86" s="45" t="str">
+      <x:c r="I86" s="62" t="str">
         <x:v>通信增量 ms</x:v>
       </x:c>
-      <x:c r="J86" s="45" t="str">
+      <x:c r="J86" s="62" t="str">
         <x:v>暴露系数</x:v>
       </x:c>
-      <x:c r="K86" s="45" t="str">
+      <x:c r="K86" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="L86" s="45" t="str">
+      <x:c r="L86" s="62" t="str">
         <x:v>公式口径</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="23" customHeight="1">
+    <x:row r="87" ht="15" customHeight="1">
       <x:c r="A87" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -9251,11 +9286,11 @@
         <x:f>(K53*2^20)/1e9</x:f>
         <x:v>0.005505024</x:v>
       </x:c>
-      <x:c r="E87" s="51" t="n">
+      <x:c r="E87" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F87" s="52" t="n">
+      <x:c r="F87" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G87" s="34" t="n">
@@ -9270,7 +9305,7 @@
         <x:f>G87*F87*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0.006116693333333334</x:v>
       </x:c>
-      <x:c r="J87" s="52" t="n">
+      <x:c r="J87" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K87" s="34" t="n">
@@ -9281,7 +9316,7 @@
         <x:v>原通信行 53</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="23" customHeight="1">
+    <x:row r="88" ht="15" customHeight="1">
       <x:c r="A88" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -9295,11 +9330,11 @@
         <x:f>(K54*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E88" s="51" t="n">
+      <x:c r="E88" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F88" s="52" t="n">
+      <x:c r="F88" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G88" s="34" t="n">
@@ -9314,7 +9349,7 @@
         <x:f>G88*F88*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J88" s="52" t="n">
+      <x:c r="J88" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K88" s="34" t="n">
@@ -9325,7 +9360,7 @@
         <x:v>原通信行 54</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="23" customHeight="1">
+    <x:row r="89" ht="15" customHeight="1">
       <x:c r="A89" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -9339,11 +9374,11 @@
         <x:f>(K55*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E89" s="51" t="n">
+      <x:c r="E89" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F89" s="52" t="n">
+      <x:c r="F89" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G89" s="34" t="n">
@@ -9358,7 +9393,7 @@
         <x:f>G89*F89*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J89" s="52" t="n">
+      <x:c r="J89" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K89" s="34" t="n">
@@ -9369,7 +9404,7 @@
         <x:v>原通信行 55</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="23" customHeight="1">
+    <x:row r="90" ht="15" customHeight="1">
       <x:c r="A90" s="30" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -9383,11 +9418,11 @@
         <x:f>(K56*2^20)/1e9</x:f>
         <x:v>0.217448448</x:v>
       </x:c>
-      <x:c r="E90" s="51" t="n">
+      <x:c r="E90" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F90" s="52" t="n">
+      <x:c r="F90" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G90" s="34" t="n">
@@ -9402,7 +9437,7 @@
         <x:f>G90*F90*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0.24160938666666665</x:v>
       </x:c>
-      <x:c r="J90" s="52" t="n">
+      <x:c r="J90" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K90" s="34" t="n">
@@ -9413,7 +9448,7 @@
         <x:v>原通信行 56</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="23" customHeight="1">
+    <x:row r="91" ht="15" customHeight="1">
       <x:c r="A91" s="30" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -9427,11 +9462,11 @@
         <x:f>(K57*2^20)/1e9</x:f>
         <x:v>0.072482816</x:v>
       </x:c>
-      <x:c r="E91" s="51" t="n">
+      <x:c r="E91" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F91" s="52" t="n">
+      <x:c r="F91" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G91" s="34" t="n">
@@ -9446,7 +9481,7 @@
         <x:f>G91*F91*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0.08053646222222223</x:v>
       </x:c>
-      <x:c r="J91" s="52" t="n">
+      <x:c r="J91" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K91" s="34" t="n">
@@ -9457,7 +9492,7 @@
         <x:v>原通信行 57</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="23" customHeight="1">
+    <x:row r="92" ht="15" customHeight="1">
       <x:c r="A92" s="30" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -9471,11 +9506,11 @@
         <x:f>(K58*2^20)/1e9</x:f>
         <x:v>0.040370176</x:v>
       </x:c>
-      <x:c r="E92" s="51" t="n">
+      <x:c r="E92" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F92" s="52" t="n">
+      <x:c r="F92" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G92" s="34" t="n">
@@ -9490,7 +9525,7 @@
         <x:f>G92*F92*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0.04485575111111112</x:v>
       </x:c>
-      <x:c r="J92" s="52" t="n">
+      <x:c r="J92" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K92" s="34" t="n">
@@ -9501,7 +9536,7 @@
         <x:v>原通信行 58</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="23" customHeight="1">
+    <x:row r="93" ht="15" customHeight="1">
       <x:c r="A93" s="30" t="str">
         <x:v>O Proj TP</x:v>
       </x:c>
@@ -9515,11 +9550,11 @@
         <x:f>(K59*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E93" s="51" t="n">
+      <x:c r="E93" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F93" s="52" t="n">
+      <x:c r="F93" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G93" s="34" t="n">
@@ -9534,7 +9569,7 @@
         <x:f>G93*F93*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J93" s="52" t="n">
+      <x:c r="J93" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K93" s="34" t="n">
@@ -9545,7 +9580,7 @@
         <x:v>原通信行 59</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="23" customHeight="1">
+    <x:row r="94" ht="15" customHeight="1">
       <x:c r="A94" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -9559,11 +9594,11 @@
         <x:f>(K60*2^20)/1e9</x:f>
         <x:v>0.002064384</x:v>
       </x:c>
-      <x:c r="E94" s="51" t="n">
+      <x:c r="E94" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F94" s="52" t="n">
+      <x:c r="F94" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G94" s="34" t="n">
@@ -9578,7 +9613,7 @@
         <x:f>G94*F94*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0.00229376</x:v>
       </x:c>
-      <x:c r="J94" s="52" t="n">
+      <x:c r="J94" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K94" s="34" t="n">
@@ -9589,7 +9624,7 @@
         <x:v>原通信行 60</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="23" customHeight="1">
+    <x:row r="95" ht="15" customHeight="1">
       <x:c r="A95" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -9603,11 +9638,11 @@
         <x:f>(IF(F61=2,E61/6144*H61*(ROUNDUP((ROUNDUP(6144*F61/32,0)*32+32)/480,0)*512),NA()))/1e9</x:f>
         <x:v>0.226623488</x:v>
       </x:c>
-      <x:c r="E95" s="51" t="n">
+      <x:c r="E95" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F95" s="52" t="n">
+      <x:c r="F95" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G95" s="34" t="n">
@@ -9622,7 +9657,7 @@
         <x:f>G95*F95*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0.2518038755555556</x:v>
       </x:c>
-      <x:c r="J95" s="52" t="n">
+      <x:c r="J95" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K95" s="34" t="n">
@@ -9633,7 +9668,7 @@
         <x:v>原通信行 61</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="23" customHeight="1">
+    <x:row r="96" ht="15" customHeight="1">
       <x:c r="A96" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -9647,11 +9682,11 @@
         <x:f>(IF(F62=2,K62*2^20+E62/6144*H62*32,NA()))/1e9</x:f>
         <x:v>0.20973568</x:v>
       </x:c>
-      <x:c r="E96" s="51" t="n">
+      <x:c r="E96" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F96" s="52" t="n">
+      <x:c r="F96" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G96" s="34" t="n">
@@ -9666,7 +9701,7 @@
         <x:f>G96*F96*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0.23303964444444444</x:v>
       </x:c>
-      <x:c r="J96" s="52" t="n">
+      <x:c r="J96" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K96" s="34" t="n">
@@ -9677,7 +9712,7 @@
         <x:v>原通信行 62</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="23" customHeight="1">
+    <x:row r="97" ht="15" customHeight="1">
       <x:c r="A97" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -9691,11 +9726,11 @@
         <x:f>(K63*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E97" s="51" t="n">
+      <x:c r="E97" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F97" s="52" t="n">
+      <x:c r="F97" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G97" s="34" t="n">
@@ -9710,7 +9745,7 @@
         <x:f>G97*F97*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J97" s="52" t="n">
+      <x:c r="J97" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K97" s="34" t="n">
@@ -9721,7 +9756,7 @@
         <x:v>原通信行 63</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="23" customHeight="1">
+    <x:row r="98" ht="15" customHeight="1">
       <x:c r="A98" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -9735,11 +9770,11 @@
         <x:f>(K64*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E98" s="51" t="n">
+      <x:c r="E98" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F98" s="52" t="n">
+      <x:c r="F98" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G98" s="34" t="n">
@@ -9754,7 +9789,7 @@
         <x:f>G98*F98*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J98" s="52" t="n">
+      <x:c r="J98" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K98" s="34" t="n">
@@ -9765,7 +9800,7 @@
         <x:v>原通信行 64</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="23" customHeight="1">
+    <x:row r="99" ht="15" customHeight="1">
       <x:c r="A99" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -9779,11 +9814,11 @@
         <x:f>(K65*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E99" s="51" t="n">
+      <x:c r="E99" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F99" s="52" t="n">
+      <x:c r="F99" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G99" s="34" t="n">
@@ -9798,7 +9833,7 @@
         <x:f>G99*F99*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J99" s="52" t="n">
+      <x:c r="J99" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K99" s="34" t="n">
@@ -9809,7 +9844,7 @@
         <x:v>原通信行 65</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="23" customHeight="1">
+    <x:row r="100" ht="15" customHeight="1">
       <x:c r="A100" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -9823,11 +9858,11 @@
         <x:f>(K66*2^20)/1e9</x:f>
         <x:v>0.209190912</x:v>
       </x:c>
-      <x:c r="E100" s="51" t="n">
+      <x:c r="E100" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F100" s="52" t="n">
+      <x:c r="F100" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G100" s="34" t="n">
@@ -9842,7 +9877,7 @@
         <x:f>G100*F100*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0.23243434666666674</x:v>
       </x:c>
-      <x:c r="J100" s="52" t="n">
+      <x:c r="J100" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K100" s="34" t="n">
@@ -9853,7 +9888,7 @@
         <x:v>原通信行 66</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="23" customHeight="1">
+    <x:row r="101" ht="15" customHeight="1">
       <x:c r="A101" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -9867,11 +9902,11 @@
         <x:f>(K67*2^20)/1e9</x:f>
         <x:v>0.209190912</x:v>
       </x:c>
-      <x:c r="E101" s="51" t="n">
+      <x:c r="E101" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F101" s="52" t="n">
+      <x:c r="F101" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G101" s="34" t="n">
@@ -9886,7 +9921,7 @@
         <x:f>G101*F101*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0.23243434666666674</x:v>
       </x:c>
-      <x:c r="J101" s="52" t="n">
+      <x:c r="J101" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K101" s="34" t="n">
@@ -9897,7 +9932,7 @@
         <x:v>原通信行 67</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="23" customHeight="1">
+    <x:row r="102" ht="15" customHeight="1">
       <x:c r="A102" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -9911,11 +9946,11 @@
         <x:f>(K68*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E102" s="51" t="n">
+      <x:c r="E102" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F102" s="52" t="n">
+      <x:c r="F102" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G102" s="34" t="n">
@@ -9930,7 +9965,7 @@
         <x:f>G102*F102*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J102" s="52" t="n">
+      <x:c r="J102" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K102" s="34" t="n">
@@ -9941,7 +9976,7 @@
         <x:v>原通信行 68</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="23" customHeight="1">
+    <x:row r="103" ht="15" customHeight="1">
       <x:c r="A103" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -9955,11 +9990,11 @@
         <x:f>(K69*2^20)/1e9</x:f>
         <x:v>0.002752512</x:v>
       </x:c>
-      <x:c r="E103" s="51" t="n">
+      <x:c r="E103" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F103" s="52" t="n">
+      <x:c r="F103" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G103" s="34" t="n">
@@ -9974,7 +10009,7 @@
         <x:f>G103*F103*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0.003058346666666667</x:v>
       </x:c>
-      <x:c r="J103" s="52" t="n">
+      <x:c r="J103" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K103" s="34" t="n">
@@ -9985,7 +10020,7 @@
         <x:v>原通信行 69</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="23" customHeight="1">
+    <x:row r="104" ht="15" customHeight="1">
       <x:c r="A104" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -9999,11 +10034,11 @@
         <x:f>(K70*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E104" s="51" t="n">
+      <x:c r="E104" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F104" s="52" t="n">
+      <x:c r="F104" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G104" s="34" t="n">
@@ -10018,7 +10053,7 @@
         <x:f>G104*F104*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J104" s="52" t="n">
+      <x:c r="J104" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K104" s="34" t="n">
@@ -10029,7 +10064,7 @@
         <x:v>原通信行 70</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="23" customHeight="1">
+    <x:row r="105" ht="15" customHeight="1">
       <x:c r="A105" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -10043,11 +10078,11 @@
         <x:f>(K71*2^20)/1e9</x:f>
         <x:v>0.002752512</x:v>
       </x:c>
-      <x:c r="E105" s="51" t="n">
+      <x:c r="E105" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F105" s="52" t="n">
+      <x:c r="F105" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G105" s="34" t="n">
@@ -10062,7 +10097,7 @@
         <x:f>G105*F105*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0.003058346666666667</x:v>
       </x:c>
-      <x:c r="J105" s="52" t="n">
+      <x:c r="J105" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K105" s="34" t="n">
@@ -10073,7 +10108,7 @@
         <x:v>原通信行 71</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="23" customHeight="1">
+    <x:row r="106" ht="15" customHeight="1">
       <x:c r="A106" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -10087,11 +10122,11 @@
         <x:f>(K72*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E106" s="51" t="n">
+      <x:c r="E106" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F106" s="52" t="n">
+      <x:c r="F106" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G106" s="34" t="n">
@@ -10106,7 +10141,7 @@
         <x:f>G106*F106*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J106" s="52" t="n">
+      <x:c r="J106" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K106" s="34" t="n">
@@ -10117,7 +10152,7 @@
         <x:v>原通信行 72</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="23" customHeight="1">
+    <x:row r="107" ht="15" customHeight="1">
       <x:c r="A107" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -10131,11 +10166,11 @@
         <x:f>(K73*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E107" s="51" t="n">
+      <x:c r="E107" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F107" s="52" t="n">
+      <x:c r="F107" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G107" s="34" t="n">
@@ -10150,7 +10185,7 @@
         <x:f>G107*F107*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J107" s="52" t="n">
+      <x:c r="J107" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K107" s="34" t="n">
@@ -10161,7 +10196,7 @@
         <x:v>原通信行 73</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="23" customHeight="1">
+    <x:row r="108" ht="15" customHeight="1">
       <x:c r="A108" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -10175,11 +10210,11 @@
         <x:f>(K74*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E108" s="51" t="n">
+      <x:c r="E108" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F108" s="52" t="n">
+      <x:c r="F108" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G108" s="34" t="n">
@@ -10194,7 +10229,7 @@
         <x:f>G108*F108*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J108" s="52" t="n">
+      <x:c r="J108" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K108" s="34" t="n">
@@ -10205,7 +10240,7 @@
         <x:v>原通信行 74</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="23" customHeight="1">
+    <x:row r="109" ht="15" customHeight="1">
       <x:c r="A109" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -10219,11 +10254,11 @@
         <x:f>(IF(E61=0,0,H61*ROUNDUP(256/G61,0)*(G61-1)*32))/1e9</x:f>
         <x:v>0.000544768</x:v>
       </x:c>
-      <x:c r="E109" s="51" t="n">
+      <x:c r="E109" s="64" t="n">
         <x:f>$H$81</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F109" s="52" t="n">
+      <x:c r="F109" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G109" s="34" t="n">
@@ -10238,7 +10273,7 @@
         <x:f>G109*F109*$D$81*$B$81/(1-$B$81)</x:f>
         <x:v>0.0006052977777777778</x:v>
       </x:c>
-      <x:c r="J109" s="52" t="n">
+      <x:c r="J109" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K109" s="34" t="n">
@@ -10249,36 +10284,36 @@
         <x:v>额外控制量</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="23" customHeight="1">
-      <x:c r="A110" s="53" t="str">
+    <x:row r="110" ht="15" customHeight="1">
+      <x:c r="A110" s="40" t="str">
         <x:v>所列事件串行相加</x:v>
       </x:c>
-      <x:c r="B110" s="53"/>
-      <x:c r="C110" s="53"/>
-      <x:c r="D110" s="54" t="n">
+      <x:c r="B110" s="40"/>
+      <x:c r="C110" s="40"/>
+      <x:c r="D110" s="41" t="n">
         <x:f>SUM(D87:D109)</x:f>
         <x:v>1.1986616319999999</x:v>
       </x:c>
-      <x:c r="E110" s="54"/>
-      <x:c r="F110" s="53"/>
-      <x:c r="G110" s="54" t="n">
+      <x:c r="E110" s="40"/>
+      <x:c r="F110" s="40"/>
+      <x:c r="G110" s="41" t="n">
         <x:f>SUM(G87:G109)</x:f>
         <x:v>11.98661632</x:v>
       </x:c>
-      <x:c r="H110" s="54" t="n">
+      <x:c r="H110" s="41" t="n">
         <x:f>SUM(H87:H109)</x:f>
         <x:v>13.318462577777776</x:v>
       </x:c>
-      <x:c r="I110" s="54" t="n">
+      <x:c r="I110" s="41" t="n">
         <x:f>SUM(I87:I109)</x:f>
         <x:v>1.331846257777778</x:v>
       </x:c>
-      <x:c r="J110" s="53"/>
-      <x:c r="K110" s="54" t="n">
+      <x:c r="J110" s="40"/>
+      <x:c r="K110" s="41" t="n">
         <x:f>SUM(K87:K109)</x:f>
         <x:v>1.331846257777778</x:v>
       </x:c>
-      <x:c r="L110" s="53"/>
+      <x:c r="L110" s="40"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="L83:L83">

--- a/models/glm-5.3/glm-5.3-analysis.xlsx
+++ b/models/glm-5.3/glm-5.3-analysis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R204d6852ff0a4583"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rf48a2cab44884f43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R9eee41b5e0004a89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Ra2af6e74f0bb4d4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rb99f4f1825fb4e0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R17dba83b26004568"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -145,7 +145,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="81">
+  <x:cellXfs count="82">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -335,6 +335,9 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -365,7 +368,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -375,7 +378,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -385,7 +388,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -395,7 +398,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -10568,7 +10571,7 @@
       <x:c r="W4" s="30"/>
       <x:c r="X4" s="30"/>
     </x:row>
-    <x:row r="5" ht="22" customHeight="1">
+    <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="30" t="str">
         <x:v>每 P DP 请求数</x:v>
       </x:c>
@@ -10577,16 +10580,18 @@
       </x:c>
       <x:c r="C5" s="30"/>
       <x:c r="D5" s="30"/>
-      <x:c r="E5" s="30" t="str">
-        <x:v>P EP 组数</x:v>
+      <x:c r="E5" s="79" t="str">
+        <x:v>P deployment
+count</x:v>
       </x:c>
       <x:c r="F5" s="66" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="30"/>
       <x:c r="H5" s="30"/>
-      <x:c r="I5" s="30" t="str">
-        <x:v>D EP 组数</x:v>
+      <x:c r="I5" s="79" t="str">
+        <x:v>D deployment
+count</x:v>
       </x:c>
       <x:c r="J5" s="66" t="n">
         <x:v>1</x:v>
@@ -10704,25 +10709,28 @@
       <x:c r="W8" s="30"/>
       <x:c r="X8" s="30"/>
     </x:row>
-    <x:row r="9" ht="22" customHeight="1">
-      <x:c r="A9" s="30" t="str">
-        <x:v>每周期错峰批数</x:v>
+    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="A9" s="79" t="str">
+        <x:v>KV bursts
+per interval</x:v>
       </x:c>
       <x:c r="B9" s="66" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="30"/>
       <x:c r="D9" s="30"/>
-      <x:c r="E9" s="30" t="str">
-        <x:v>通信共享比例</x:v>
+      <x:c r="E9" s="79" t="str">
+        <x:v>EP shared
+resource fraction</x:v>
       </x:c>
       <x:c r="F9" s="68" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="30"/>
       <x:c r="H9" s="30"/>
-      <x:c r="I9" s="30" t="str">
-        <x:v>关键路径暴露率</x:v>
+      <x:c r="I9" s="79" t="str">
+        <x:v>EP exposed
+comm fraction</x:v>
       </x:c>
       <x:c r="J9" s="68" t="n">
         <x:v>1</x:v>
@@ -10780,9 +10788,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="30"/>
-      <x:c r="D11" s="30" t="str">
-        <x:v>TTFT 暂作 P 批次间隔；步间隔＝TPOT×平均产出。每周期 1 批表示各 P DP 同步交接。</x:v>
-      </x:c>
+      <x:c r="D11" s="30" t="str"/>
       <x:c r="E11" s="30"/>
       <x:c r="F11" s="30"/>
       <x:c r="G11" s="30"/>
@@ -10805,7 +10811,9 @@
       <x:c r="X11" s="30"/>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="30"/>
+      <x:c r="A12" s="30" t="str">
+        <x:v>P = Prefill，D = Decode。通常只需修改带宽、请求数和 TTFT/TPOT；附加假设可保持默认。</x:v>
+      </x:c>
       <x:c r="B12" s="30"/>
       <x:c r="C12" s="30"/>
       <x:c r="D12" s="30"/>
@@ -10831,7 +10839,9 @@
       <x:c r="X12" s="30"/>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
-      <x:c r="A13" s="30"/>
+      <x:c r="A13" s="30" t="str">
+        <x:v>Total overhead 表示基线 60 秒工作量的额外耗时；TTFT 在这里作为 KV 批次到达间隔。</x:v>
+      </x:c>
       <x:c r="B13" s="30"/>
       <x:c r="C13" s="30"/>
       <x:c r="D13" s="30"/>
@@ -10910,22 +10920,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G15" s="30"/>
-      <x:c r="H15" s="30" t="str">
-        <x:v>黄色为输入；模型 / EP 带宽可在下表逐项覆盖。</x:v>
-      </x:c>
-      <x:c r="I15" s="30"/>
-      <x:c r="J15" s="30"/>
-      <x:c r="K15" s="30"/>
-      <x:c r="L15" s="30"/>
-      <x:c r="M15" s="30"/>
-      <x:c r="N15" s="30"/>
-      <x:c r="O15" s="30"/>
-      <x:c r="P15" s="30"/>
-      <x:c r="Q15" s="30"/>
-      <x:c r="R15" s="30"/>
-      <x:c r="S15" s="30"/>
-      <x:c r="T15" s="30"/>
-      <x:c r="U15" s="30"/>
+      <x:c r="H15" s="81" t="str">
+        <x:v>Default: P = D = 1; KV bursts = 1; shared / exposed fractions = 100%.</x:v>
+      </x:c>
+      <x:c r="I15" s="81"/>
+      <x:c r="J15" s="81"/>
+      <x:c r="K15" s="81"/>
+      <x:c r="L15" s="81"/>
+      <x:c r="M15" s="81"/>
+      <x:c r="N15" s="81"/>
+      <x:c r="O15" s="81"/>
+      <x:c r="P15" s="81"/>
+      <x:c r="Q15" s="81"/>
+      <x:c r="R15" s="81"/>
+      <x:c r="S15" s="81"/>
+      <x:c r="T15" s="81"/>
+      <x:c r="U15" s="81"/>
       <x:c r="V15" s="30"/>
       <x:c r="W15" s="30"/>
       <x:c r="X15" s="30"/>
@@ -10948,22 +10958,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G16" s="30"/>
-      <x:c r="H16" s="30" t="str">
-        <x:v>时间增量针对基线 60 秒工作量；不表示实测吞吐或 P99。</x:v>
-      </x:c>
-      <x:c r="I16" s="30"/>
-      <x:c r="J16" s="30"/>
-      <x:c r="K16" s="30"/>
-      <x:c r="L16" s="30"/>
-      <x:c r="M16" s="30"/>
-      <x:c r="N16" s="30"/>
-      <x:c r="O16" s="30"/>
-      <x:c r="P16" s="30"/>
-      <x:c r="Q16" s="30"/>
-      <x:c r="R16" s="30"/>
-      <x:c r="S16" s="30"/>
-      <x:c r="T16" s="30"/>
-      <x:c r="U16" s="30"/>
+      <x:c r="H16" s="81" t="str">
+        <x:v>Deployment count：完整 EP 部署的套数；EP32 每套 32 卡，EP256 每套 256 卡。</x:v>
+      </x:c>
+      <x:c r="I16" s="81"/>
+      <x:c r="J16" s="81"/>
+      <x:c r="K16" s="81"/>
+      <x:c r="L16" s="81"/>
+      <x:c r="M16" s="81"/>
+      <x:c r="N16" s="81"/>
+      <x:c r="O16" s="81"/>
+      <x:c r="P16" s="81"/>
+      <x:c r="Q16" s="81"/>
+      <x:c r="R16" s="81"/>
+      <x:c r="S16" s="81"/>
+      <x:c r="T16" s="81"/>
+      <x:c r="U16" s="81"/>
       <x:c r="V16" s="30"/>
       <x:c r="W16" s="30"/>
       <x:c r="X16" s="30"/>
@@ -10986,22 +10996,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G17" s="30"/>
-      <x:c r="H17" s="30" t="str">
-        <x:v>TTFT 只用于到达节奏，本页估算 D 侧 TPOT；P 耗时仍见原表。</x:v>
-      </x:c>
-      <x:c r="I17" s="30"/>
-      <x:c r="J17" s="30"/>
-      <x:c r="K17" s="30"/>
-      <x:c r="L17" s="30"/>
-      <x:c r="M17" s="30"/>
-      <x:c r="N17" s="30"/>
-      <x:c r="O17" s="30"/>
-      <x:c r="P17" s="30"/>
-      <x:c r="Q17" s="30"/>
-      <x:c r="R17" s="30"/>
-      <x:c r="S17" s="30"/>
-      <x:c r="T17" s="30"/>
-      <x:c r="U17" s="30"/>
+      <x:c r="H17" s="81" t="str">
+        <x:v>Shared resource fraction：通信中与 KV 竞争同一资源的比例。100% = 全部；0% = 资源独立。</x:v>
+      </x:c>
+      <x:c r="I17" s="81"/>
+      <x:c r="J17" s="81"/>
+      <x:c r="K17" s="81"/>
+      <x:c r="L17" s="81"/>
+      <x:c r="M17" s="81"/>
+      <x:c r="N17" s="81"/>
+      <x:c r="O17" s="81"/>
+      <x:c r="P17" s="81"/>
+      <x:c r="Q17" s="81"/>
+      <x:c r="R17" s="81"/>
+      <x:c r="S17" s="81"/>
+      <x:c r="T17" s="81"/>
+      <x:c r="U17" s="81"/>
       <x:c r="V17" s="30"/>
       <x:c r="W17" s="30"/>
       <x:c r="X17" s="30"/>
@@ -11018,22 +11028,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G18" s="30"/>
-      <x:c r="H18" s="30" t="str">
-        <x:v>全 EP＝该步所有等效 EP 通信段都在 KV 窗口内；不代表整步持续时间都重叠。</x:v>
-      </x:c>
-      <x:c r="I18" s="30"/>
-      <x:c r="J18" s="30"/>
-      <x:c r="K18" s="30"/>
-      <x:c r="L18" s="30"/>
-      <x:c r="M18" s="30"/>
-      <x:c r="N18" s="30"/>
-      <x:c r="O18" s="30"/>
-      <x:c r="P18" s="30"/>
-      <x:c r="Q18" s="30"/>
-      <x:c r="R18" s="30"/>
-      <x:c r="S18" s="30"/>
-      <x:c r="T18" s="30"/>
-      <x:c r="U18" s="30"/>
+      <x:c r="H18" s="81" t="str">
+        <x:v>Exposed communication fraction：通信增时最终计入 forward 的比例；被计算遮住的部分不计入。</x:v>
+      </x:c>
+      <x:c r="I18" s="81"/>
+      <x:c r="J18" s="81"/>
+      <x:c r="K18" s="81"/>
+      <x:c r="L18" s="81"/>
+      <x:c r="M18" s="81"/>
+      <x:c r="N18" s="81"/>
+      <x:c r="O18" s="81"/>
+      <x:c r="P18" s="81"/>
+      <x:c r="Q18" s="81"/>
+      <x:c r="R18" s="81"/>
+      <x:c r="S18" s="81"/>
+      <x:c r="T18" s="81"/>
+      <x:c r="U18" s="81"/>
       <x:c r="V18" s="30"/>
       <x:c r="W18" s="30"/>
       <x:c r="X18" s="30"/>
@@ -11046,20 +11056,22 @@
       <x:c r="E19" s="30"/>
       <x:c r="F19" s="30"/>
       <x:c r="G19" s="30"/>
-      <x:c r="H19" s="30"/>
-      <x:c r="I19" s="30"/>
-      <x:c r="J19" s="30"/>
-      <x:c r="K19" s="30"/>
-      <x:c r="L19" s="30"/>
-      <x:c r="M19" s="30"/>
-      <x:c r="N19" s="30"/>
-      <x:c r="O19" s="30"/>
-      <x:c r="P19" s="30"/>
-      <x:c r="Q19" s="30"/>
-      <x:c r="R19" s="30"/>
-      <x:c r="S19" s="30"/>
-      <x:c r="T19" s="30"/>
-      <x:c r="U19" s="30"/>
+      <x:c r="H19" s="81" t="str">
+        <x:v>KV bursts per interval：一批 KV 均分成 m 次、等间隔发送；m = 2 时每次一半，总量不变。</x:v>
+      </x:c>
+      <x:c r="I19" s="81"/>
+      <x:c r="J19" s="81"/>
+      <x:c r="K19" s="81"/>
+      <x:c r="L19" s="81"/>
+      <x:c r="M19" s="81"/>
+      <x:c r="N19" s="81"/>
+      <x:c r="O19" s="81"/>
+      <x:c r="P19" s="81"/>
+      <x:c r="Q19" s="81"/>
+      <x:c r="R19" s="81"/>
+      <x:c r="S19" s="81"/>
+      <x:c r="T19" s="81"/>
+      <x:c r="U19" s="81"/>
       <x:c r="V19" s="30"/>
       <x:c r="W19" s="30"/>
       <x:c r="X19" s="30"/>
@@ -11072,20 +11084,22 @@
       <x:c r="E20" s="30"/>
       <x:c r="F20" s="30"/>
       <x:c r="G20" s="30"/>
-      <x:c r="H20" s="30"/>
-      <x:c r="I20" s="30"/>
-      <x:c r="J20" s="30"/>
-      <x:c r="K20" s="30"/>
-      <x:c r="L20" s="30"/>
-      <x:c r="M20" s="30"/>
-      <x:c r="N20" s="30"/>
-      <x:c r="O20" s="30"/>
-      <x:c r="P20" s="30"/>
-      <x:c r="Q20" s="30"/>
-      <x:c r="R20" s="30"/>
-      <x:c r="S20" s="30"/>
-      <x:c r="T20" s="30"/>
-      <x:c r="U20" s="30"/>
+      <x:c r="H20" s="81" t="str">
+        <x:v>Temporal overlap 由 KV 窗口自动计算；没有 profiling 时，不必另猜 shared / exposed 两个比例。</x:v>
+      </x:c>
+      <x:c r="I20" s="81"/>
+      <x:c r="J20" s="81"/>
+      <x:c r="K20" s="81"/>
+      <x:c r="L20" s="81"/>
+      <x:c r="M20" s="81"/>
+      <x:c r="N20" s="81"/>
+      <x:c r="O20" s="81"/>
+      <x:c r="P20" s="81"/>
+      <x:c r="Q20" s="81"/>
+      <x:c r="R20" s="81"/>
+      <x:c r="S20" s="81"/>
+      <x:c r="T20" s="81"/>
+      <x:c r="U20" s="81"/>
       <x:c r="V20" s="30"/>
       <x:c r="W20" s="30"/>
       <x:c r="X20" s="30"/>
@@ -11153,11 +11167,13 @@
       <x:c r="L22" s="73" t="str">
         <x:v>产出 tokens/步</x:v>
       </x:c>
-      <x:c r="M22" s="73" t="str">
-        <x:v>共享比例</x:v>
-      </x:c>
-      <x:c r="N22" s="73" t="str">
-        <x:v>暴露率</x:v>
+      <x:c r="M22" s="18" t="str">
+        <x:v>EP shared
+resource fraction</x:v>
+      </x:c>
+      <x:c r="N22" s="18" t="str">
+        <x:v>EP exposed
+comm fraction</x:v>
       </x:c>
       <x:c r="O22" s="73" t="str">
         <x:v>配置条件</x:v>
@@ -11436,8 +11452,9 @@
       <x:c r="K29" s="73" t="str">
         <x:v>重叠层调用 次/min</x:v>
       </x:c>
-      <x:c r="L29" s="73" t="str">
-        <x:v>60s 工作增时 ms</x:v>
+      <x:c r="L29" s="18" t="str">
+        <x:v>Total overhead
+ms/60s</x:v>
       </x:c>
       <x:c r="M29" s="73" t="str">
         <x:v>平均 TPOT 增量 μs</x:v>
@@ -13434,8 +13451,9 @@
       <x:c r="U59" s="73" t="str">
         <x:v>基线 FW/min</x:v>
       </x:c>
-      <x:c r="V59" s="73" t="str">
-        <x:v>60s 工作增时 ms</x:v>
+      <x:c r="V59" s="18" t="str">
+        <x:v>Total overhead
+ms/60s</x:v>
       </x:c>
       <x:c r="W59" s="73" t="str">
         <x:v>输入 / 调度状态</x:v>

--- a/models/glm-5.3/glm-5.3-analysis.xlsx
+++ b/models/glm-5.3/glm-5.3-analysis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Ra2af6e74f0bb4d4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rb99f4f1825fb4e0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R17dba83b26004568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R384ae4fa64f9491b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rfe8fe7c3f5684f97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R506e9c7113c24597"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="13">
+  <x:numFmts count="15">
     <x:numFmt numFmtId="200" formatCode="0.##"/>
     <x:numFmt numFmtId="201" formatCode="0.0000"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.####"/>
@@ -29,6 +29,8 @@
     <x:numFmt numFmtId="210" formatCode="#,##0.000"/>
     <x:numFmt numFmtId="211" formatCode="#,##0.000000"/>
     <x:numFmt numFmtId="212" formatCode="0.000000%"/>
+    <x:numFmt numFmtId="213" formatCode="0.00000000%"/>
+    <x:numFmt numFmtId="214" formatCode="[=0]0.000000%;[&lt;0.00000001]&quot;&lt;0.000001%&quot;;0.000000%"/>
   </x:numFmts>
   <x:fonts count="5">
     <x:font>
@@ -58,7 +60,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -110,6 +112,16 @@
         <x:fgColor rgb="FFD9E2F3"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="3">
     <x:border/>
@@ -145,7 +157,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="82">
+  <x:cellXfs count="90">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -337,6 +349,30 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="214" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -10453,7 +10489,7 @@
     <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="30" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="21" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
@@ -11468,7 +11504,10 @@
       <x:c r="P29" s="73" t="str">
         <x:v>最低 EP GB/s</x:v>
       </x:c>
-      <x:c r="Q29" s="30"/>
+      <x:c r="Q29" s="88" t="str">
+        <x:v>Decode throughput
+loss (%)</x:v>
+      </x:c>
       <x:c r="R29" s="30"/>
       <x:c r="S29" s="30"/>
       <x:c r="T29" s="30"/>
@@ -11542,7 +11581,10 @@
         <x:f>Q60</x:f>
         <x:v>381.5232</x:v>
       </x:c>
-      <x:c r="Q30" s="30"/>
+      <x:c r="Q30" s="89" t="n">
+        <x:f>IF(ISNUMBER(L30),L30/(60000+L30),IF(L30="","",L30))</x:f>
+        <x:v>0.0000014347343374794483</x:v>
+      </x:c>
       <x:c r="R30" s="30"/>
       <x:c r="S30" s="30"/>
       <x:c r="T30" s="30"/>
@@ -11616,7 +11658,10 @@
         <x:f>Q61</x:f>
         <x:v>190.7616</x:v>
       </x:c>
-      <x:c r="Q31" s="30"/>
+      <x:c r="Q31" s="89" t="n">
+        <x:f>IF(ISNUMBER(L31),L31/(60000+L31),IF(L31="","",L31))</x:f>
+        <x:v>7.173676833557481e-7</x:v>
+      </x:c>
       <x:c r="R31" s="30"/>
       <x:c r="S31" s="30"/>
       <x:c r="T31" s="30"/>
@@ -11690,7 +11735,10 @@
         <x:f>Q62</x:f>
         <x:v>95.3808</x:v>
       </x:c>
-      <x:c r="Q32" s="30"/>
+      <x:c r="Q32" s="89" t="n">
+        <x:f>IF(ISNUMBER(L32),L32/(60000+L32),IF(L32="","",L32))</x:f>
+        <x:v>3.586839703320185e-7</x:v>
+      </x:c>
       <x:c r="R32" s="30"/>
       <x:c r="S32" s="30"/>
       <x:c r="T32" s="30"/>
@@ -11764,7 +11812,10 @@
         <x:f>Q63</x:f>
         <x:v>63.5872</x:v>
       </x:c>
-      <x:c r="Q33" s="30"/>
+      <x:c r="Q33" s="89" t="n">
+        <x:f>IF(ISNUMBER(L33),L33/(60000+L33),IF(L33="","",L33))</x:f>
+        <x:v>2.3912267547783585e-7</x:v>
+      </x:c>
       <x:c r="R33" s="30"/>
       <x:c r="S33" s="30"/>
       <x:c r="T33" s="30"/>
@@ -11838,7 +11889,10 @@
         <x:f>Q64</x:f>
         <x:v>381.5232</x:v>
       </x:c>
-      <x:c r="Q34" s="30"/>
+      <x:c r="Q34" s="89" t="n">
+        <x:f>IF(ISNUMBER(L34),L34/(60000+L34),IF(L34="","",L34))</x:f>
+        <x:v>0.0000045930852798330524</x:v>
+      </x:c>
       <x:c r="R34" s="30"/>
       <x:c r="S34" s="30"/>
       <x:c r="T34" s="30"/>
@@ -11912,7 +11966,10 @@
         <x:f>Q65</x:f>
         <x:v>190.7616</x:v>
       </x:c>
-      <x:c r="Q35" s="30"/>
+      <x:c r="Q35" s="89" t="n">
+        <x:f>IF(ISNUMBER(L35),L35/(60000+L35),IF(L35="","",L35))</x:f>
+        <x:v>0.0000022965479140367353</x:v>
+      </x:c>
       <x:c r="R35" s="30"/>
       <x:c r="S35" s="30"/>
       <x:c r="T35" s="30"/>
@@ -11986,7 +12043,10 @@
         <x:f>Q66</x:f>
         <x:v>95.3808</x:v>
       </x:c>
-      <x:c r="Q36" s="30"/>
+      <x:c r="Q36" s="89" t="n">
+        <x:f>IF(ISNUMBER(L36),L36/(60000+L36),IF(L36="","",L36))</x:f>
+        <x:v>0.000001148275275552962</x:v>
+      </x:c>
       <x:c r="R36" s="30"/>
       <x:c r="S36" s="30"/>
       <x:c r="T36" s="30"/>
@@ -12060,7 +12120,10 @@
         <x:f>Q67</x:f>
         <x:v>63.5872</x:v>
       </x:c>
-      <x:c r="Q37" s="30"/>
+      <x:c r="Q37" s="89" t="n">
+        <x:f>IF(ISNUMBER(L37),L37/(60000+L37),IF(L37="","",L37))</x:f>
+        <x:v>7.655171433767776e-7</x:v>
+      </x:c>
       <x:c r="R37" s="30"/>
       <x:c r="S37" s="30"/>
       <x:c r="T37" s="30"/>
@@ -12134,7 +12197,10 @@
         <x:f>Q68</x:f>
         <x:v>381.5232</x:v>
       </x:c>
-      <x:c r="Q38" s="30"/>
+      <x:c r="Q38" s="89" t="n">
+        <x:f>IF(ISNUMBER(L38),L38/(60000+L38),IF(L38="","",L38))</x:f>
+        <x:v>0.000006124234322629933</x:v>
+      </x:c>
       <x:c r="R38" s="30"/>
       <x:c r="S38" s="30"/>
       <x:c r="T38" s="30"/>
@@ -12208,7 +12274,10 @@
         <x:f>Q69</x:f>
         <x:v>190.7616</x:v>
       </x:c>
-      <x:c r="Q39" s="30"/>
+      <x:c r="Q39" s="89" t="n">
+        <x:f>IF(ISNUMBER(L39),L39/(60000+L39),IF(L39="","",L39))</x:f>
+        <x:v>0.0000030621265379051884</x:v>
+      </x:c>
       <x:c r="R39" s="30"/>
       <x:c r="S39" s="30"/>
       <x:c r="T39" s="30"/>
@@ -12282,7 +12351,10 @@
         <x:f>Q70</x:f>
         <x:v>95.3808</x:v>
       </x:c>
-      <x:c r="Q40" s="30"/>
+      <x:c r="Q40" s="89" t="n">
+        <x:f>IF(ISNUMBER(L40),L40/(60000+L40),IF(L40="","",L40))</x:f>
+        <x:v>0.0000015310656131109166</x:v>
+      </x:c>
       <x:c r="R40" s="30"/>
       <x:c r="S40" s="30"/>
       <x:c r="T40" s="30"/>
@@ -12356,7 +12428,10 @@
         <x:f>Q71</x:f>
         <x:v>63.5872</x:v>
       </x:c>
-      <x:c r="Q41" s="30"/>
+      <x:c r="Q41" s="89" t="n">
+        <x:f>IF(ISNUMBER(L41),L41/(60000+L41),IF(L41="","",L41))</x:f>
+        <x:v>0.0000010207109296657463</x:v>
+      </x:c>
       <x:c r="R41" s="30"/>
       <x:c r="S41" s="30"/>
       <x:c r="T41" s="30"/>
@@ -12430,7 +12505,10 @@
         <x:f>Q72</x:f>
         <x:v>392.29200000000003</x:v>
       </x:c>
-      <x:c r="Q42" s="30"/>
+      <x:c r="Q42" s="89" t="n">
+        <x:f>IF(ISNUMBER(L42),L42/(60000+L42),IF(L42="","",L42))</x:f>
+        <x:v>0.000001475211947762934</x:v>
+      </x:c>
       <x:c r="R42" s="30"/>
       <x:c r="S42" s="30"/>
       <x:c r="T42" s="30"/>
@@ -12504,7 +12582,10 @@
         <x:f>Q73</x:f>
         <x:v>196.14600000000002</x:v>
       </x:c>
-      <x:c r="Q43" s="30"/>
+      <x:c r="Q43" s="89" t="n">
+        <x:f>IF(ISNUMBER(L43),L43/(60000+L43),IF(L43="","",L43))</x:f>
+        <x:v>7.37606517944441e-7</x:v>
+      </x:c>
       <x:c r="R43" s="30"/>
       <x:c r="S43" s="30"/>
       <x:c r="T43" s="30"/>
@@ -12578,7 +12659,10 @@
         <x:f>Q74</x:f>
         <x:v>98.07300000000001</x:v>
       </x:c>
-      <x:c r="Q44" s="30"/>
+      <x:c r="Q44" s="89" t="n">
+        <x:f>IF(ISNUMBER(L44),L44/(60000+L44),IF(L44="","",L44))</x:f>
+        <x:v>3.688033949881145e-7</x:v>
+      </x:c>
       <x:c r="R44" s="30"/>
       <x:c r="S44" s="30"/>
       <x:c r="T44" s="30"/>
@@ -12652,7 +12736,10 @@
         <x:f>Q75</x:f>
         <x:v>65.382</x:v>
       </x:c>
-      <x:c r="Q45" s="30"/>
+      <x:c r="Q45" s="89" t="n">
+        <x:f>IF(ISNUMBER(L45),L45/(60000+L45),IF(L45="","",L45))</x:f>
+        <x:v>2.4586896021784544e-7</x:v>
+      </x:c>
       <x:c r="R45" s="30"/>
       <x:c r="S45" s="30"/>
       <x:c r="T45" s="30"/>
@@ -12726,7 +12813,10 @@
         <x:f>Q76</x:f>
         <x:v>392.29200000000003</x:v>
       </x:c>
-      <x:c r="Q46" s="30"/>
+      <x:c r="Q46" s="89" t="n">
+        <x:f>IF(ISNUMBER(L46),L46/(60000+L46),IF(L46="","",L46))</x:f>
+        <x:v>0.0000047227244309719</x:v>
+      </x:c>
       <x:c r="R46" s="30"/>
       <x:c r="S46" s="30"/>
       <x:c r="T46" s="30"/>
@@ -12800,7 +12890,10 @@
         <x:f>Q77</x:f>
         <x:v>196.14600000000002</x:v>
       </x:c>
-      <x:c r="Q47" s="30"/>
+      <x:c r="Q47" s="89" t="n">
+        <x:f>IF(ISNUMBER(L47),L47/(60000+L47),IF(L47="","",L47))</x:f>
+        <x:v>0.0000023613677915306294</x:v>
+      </x:c>
       <x:c r="R47" s="30"/>
       <x:c r="S47" s="30"/>
       <x:c r="T47" s="30"/>
@@ -12874,7 +12967,10 @@
         <x:f>Q78</x:f>
         <x:v>98.07300000000001</x:v>
       </x:c>
-      <x:c r="Q48" s="30"/>
+      <x:c r="Q48" s="89" t="n">
+        <x:f>IF(ISNUMBER(L48),L48/(60000+L48),IF(L48="","",L48))</x:f>
+        <x:v>0.0000011806852897814223</x:v>
+      </x:c>
       <x:c r="R48" s="30"/>
       <x:c r="S48" s="30"/>
       <x:c r="T48" s="30"/>
@@ -12948,7 +13044,10 @@
         <x:f>Q79</x:f>
         <x:v>65.382</x:v>
       </x:c>
-      <x:c r="Q49" s="30"/>
+      <x:c r="Q49" s="89" t="n">
+        <x:f>IF(ISNUMBER(L49),L49/(60000+L49),IF(L49="","",L49))</x:f>
+        <x:v>7.871238363027931e-7</x:v>
+      </x:c>
       <x:c r="R49" s="30"/>
       <x:c r="S49" s="30"/>
       <x:c r="T49" s="30"/>
@@ -13022,7 +13121,10 @@
         <x:f>Q80</x:f>
         <x:v>392.29200000000003</x:v>
       </x:c>
-      <x:c r="Q50" s="30"/>
+      <x:c r="Q50" s="89" t="n">
+        <x:f>IF(ISNUMBER(L50),L50/(60000+L50),IF(L50="","",L50))</x:f>
+        <x:v>0.000006297093429192404</x:v>
+      </x:c>
       <x:c r="R50" s="30"/>
       <x:c r="S50" s="30"/>
       <x:c r="T50" s="30"/>
@@ -13096,7 +13198,10 @@
         <x:f>Q81</x:f>
         <x:v>196.14600000000002</x:v>
       </x:c>
-      <x:c r="Q51" s="30"/>
+      <x:c r="Q51" s="89" t="n">
+        <x:f>IF(ISNUMBER(L51),L51/(60000+L51),IF(L51="","",L51))</x:f>
+        <x:v>0.0000031485566279738292</x:v>
+      </x:c>
       <x:c r="R51" s="30"/>
       <x:c r="S51" s="30"/>
       <x:c r="T51" s="30"/>
@@ -13170,7 +13275,10 @@
         <x:f>Q82</x:f>
         <x:v>98.07300000000001</x:v>
       </x:c>
-      <x:c r="Q52" s="30"/>
+      <x:c r="Q52" s="89" t="n">
+        <x:f>IF(ISNUMBER(L52),L52/(60000+L52),IF(L52="","",L52))</x:f>
+        <x:v>0.000001574280792343026</x:v>
+      </x:c>
       <x:c r="R52" s="30"/>
       <x:c r="S52" s="30"/>
       <x:c r="T52" s="30"/>
@@ -13244,7 +13352,10 @@
         <x:f>Q83</x:f>
         <x:v>65.382</x:v>
       </x:c>
-      <x:c r="Q53" s="30"/>
+      <x:c r="Q53" s="89" t="n">
+        <x:f>IF(ISNUMBER(L53),L53/(60000+L53),IF(L53="","",L53))</x:f>
+        <x:v>0.0000010495210789756425</x:v>
+      </x:c>
       <x:c r="R53" s="30"/>
       <x:c r="S53" s="30"/>
       <x:c r="T53" s="30"/>
@@ -13254,7 +13365,9 @@
       <x:c r="X53" s="30"/>
     </x:row>
     <x:row r="54" ht="22" customHeight="1">
-      <x:c r="A54" s="30"/>
+      <x:c r="A54" s="30" t="str">
+        <x:v>Decode throughput loss = Total overhead / (60000 + Total overhead). Fixed batch size and tokens/step; Decode stays busy.</x:v>
+      </x:c>
       <x:c r="B54" s="30"/>
       <x:c r="C54" s="30"/>
       <x:c r="D54" s="30"/>
